--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>-0.02</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>1.54</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>9.609999999999999</v>
+        <v>11.81</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>9.609999999999999</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.53</v>
+        <v>12.5</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.53</v>
@@ -8634,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="87" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>80.16</v>
+        <v>86.8</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>80.16</v>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-1.25</v>
+        <v>-1.3</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-1.84</v>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-2.19</v>
+        <v>-2.24</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-3.92</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>93.66</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>92.78</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-2.65</v>
+        <v>-2.56</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-3.33</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.05</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>57.08</v>
+        <v>57.6</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>54.27</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.59</v>
+        <v>-2.54</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.59</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-3.57</v>
+        <v>-4.42</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.57</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>53.93</v>
+        <v>54.39</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>53.93</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>6.24</v>
+        <v>7.94</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>7.24</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>8.44</v>
+        <v>10.18</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>9.02</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>69.01000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>72.36</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="91" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:19.16&gt;=10;sh:RS3:80.66&gt;=66;kc:RNG60:49.47&gt;=25;kc:RNG120:35.07&gt;=30;kc:RS5:66.31&gt;=65;cy:RNG60:46.33&gt;=25;us30:RNG60:10.19&gt;=10;vn:RS3:93.66&gt;=85</t>
+          <t>今日卖报：sh:RNG60:19.16&gt;=10;sh:RS3:80.66&gt;=66;kc:RNG60:49.47&gt;=25;kc:RNG120:35.07&gt;=30;kc:RS5:66.31&gt;=65;cy:RNG60:46.33&gt;=25;us500:RS2:86.8&gt;=85;us30:RNG60:10.19&gt;=10;vn:RS3:93.29&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.52</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>2.47</v>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>11.81</v>
+        <v>10.58</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>11.81</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.5</v>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>86.8</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>86.8</v>
@@ -8888,13 +8888,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>11</v>
+        <v>9.49</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>11</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>15.57</v>
+        <v>15.48</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>15.57</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>63.46</v>
+        <v>52.74</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>63.46</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>16.26</v>
+        <v>15.38</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>16.26</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.88</v>
+        <v>10.63</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.88</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>90.73</v>
+        <v>93.78</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>90.73</v>
@@ -9637,9 +9637,9 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="C30" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="D30" s="92" t="inlineStr">
@@ -9790,10 +9790,10 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>6.81</v>
+        <v>7.85</v>
       </c>
       <c r="C31" s="95" t="n">
-        <v>4.34</v>
+        <v>5.06</v>
       </c>
       <c r="D31" s="95" t="n">
         <v>3.13</v>
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>0.39</v>
+        <v>1.36</v>
       </c>
       <c r="C32" s="95" t="n">
-        <v>-1.62</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D32" s="95" t="n">
         <v>-2.37</v>
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>57.7</v>
+        <v>62.59</v>
       </c>
       <c r="C33" s="95" t="n">
-        <v>44.8</v>
+        <v>50.52</v>
       </c>
       <c r="D33" s="95" t="n">
         <v>43.84</v>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-0.32</v>
+        <v>-0.43</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-1.3</v>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-1.85</v>
+        <v>-1.96</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-2.24</v>
@@ -10426,13 +10426,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>93.31</v>
+        <v>78.03</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>93.29000000000001</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-1.58</v>
+        <v>-1.65</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-2.56</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.81</v>
+        <v>5.74</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.91</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>62.08</v>
+        <v>61.75</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>57.6</v>
@@ -10976,9 +10976,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.54</v>
+        <v>-2.05</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.54</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-4.42</v>
+        <v>-4.89</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-4.42</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>54.39</v>
+        <v>59.59</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>54.39</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>8.08</v>
+        <v>9.59</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>8.08</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>10.32</v>
+        <v>10.39</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>10.32</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>81.08</v>
+        <v>82.84</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>81.08</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:18.88&gt;=10;sh:RS3:84.41&gt;=66;kc:RNG60:44.82&gt;=25;kc:RNG120:35.26&gt;=30;cy:RNG60:42.08&gt;=25;us500:RS2:86.8&gt;=85;us30:RNG60:11.0&gt;=10;vn:RS3:93.31&gt;=85</t>
+          <t>今日卖报：sh:RNG60:18.88&gt;=10;sh:RS3:84.41&gt;=66;kc:RNG60:44.82&gt;=25;kc:RNG120:35.26&gt;=30;cy:RNG60:42.08&gt;=25;us500:RS2:88.26&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.21</v>
+        <v>-0.31</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.19</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>2.95</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>15.38</v>
+        <v>15.91</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>15.38</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>10.63</v>
+        <v>11.7</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>10.63</v>
@@ -9530,13 +9530,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="94" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>93.78</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>93.78</v>
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>7.85</v>
@@ -9887,7 +9887,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>1.36</v>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>63.72</v>
+        <v>62.97</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>62.59</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-0.02</v>
+        <v>-0.28</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-1.65</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.96</v>
+        <v>5.68</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>5.74</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>63.89</v>
+        <v>62.51</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>61.75</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.88</v>
+        <v>-1.26</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.05</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-4.89</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>60.21</v>
+        <v>70.47</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>59.59</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>9.59</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>11.9</v>
+        <v>11.89</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>10.39</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>86.5</v>
+        <v>86.47</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>82.84</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:19.69&gt;=10;sh:RS3:66.08&gt;=66;kc:RNG60:49.16&gt;=25;kc:RNG120:35.43&gt;=30;cy:RNG60:44.01&gt;=25;us500:RS2:88.26&gt;=85;dax30:RNG60:10.3&gt;=10</t>
+          <t>今日卖报：sh:RNG60:19.69&gt;=10;sh:RS3:66.08&gt;=66;kc:RNG60:49.16&gt;=25;kc:RNG120:35.43&gt;=30;cy:RNG60:44.01&gt;=25;us500:RS2:88.26&gt;=85;ixic:RS2:98.04&gt;=96;dax30:RNG60:10.29&gt;=10</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.28</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.31</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.08</v>
@@ -8288,9 +8288,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="91" t="inlineStr">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>10.75</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>10.75</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.01</v>
+        <v>11.85</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.01</v>
@@ -8634,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>97.03</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>97.03</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>15.91</v>
+        <v>13.25</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>15.91</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.7</v>
+        <v>11.37</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.7</v>
@@ -9530,13 +9530,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>98.04000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>98.04000000000001</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-0.28</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>6.33</v>
+        <v>6.45</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>5.68</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>67.17</v>
+        <v>67.69</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>62.51</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.44</v>
+        <v>-1.41</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.26</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-4.48</v>
+        <v>-4.44</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.53</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>74.84999999999999</v>
+        <v>75.22</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>70.47</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>9.32</v>
+        <v>9.94</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>10.38</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>10.91</v>
+        <v>11.53</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.98</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>86.90000000000001</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>86.69</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:20.19&gt;=10;sh:RS3:69.07&gt;=66;kc:RNG60:48.43&gt;=25;kc:RNG120:32.55&gt;=30;cy:RNG60:42.74&gt;=25;us500:RS2:97.03&gt;=85;us30:RNG60:10.5&gt;=10;ixic:RS2:98.04&gt;=96</t>
+          <t>今日卖报：sh:RNG60:20.19&gt;=10;sh:RS3:69.07&gt;=66;kc:RNG60:48.43&gt;=25;kc:RNG120:32.55&gt;=30;cy:RNG60:42.74&gt;=25;us30:RNG60:10.5&gt;=10</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.21</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.6</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>7.59</v>
+        <v>7.13</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>7.59</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.31</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>25.06</v>
+        <v>15.05</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>25.06</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>7.27</v>
+        <v>6.31</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>7.27</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>14.34</v>
+        <v>13.07</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>14.34</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>22.57</v>
+        <v>16.4</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>22.57</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>11.61</v>
+        <v>11.91</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>11.61</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>10.49</v>
+        <v>11.09</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>10.49</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>48.55</v>
+        <v>35.1</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>48.55</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-1.77</v>
+        <v>-1.75</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-0.02</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>5.44</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>64.12</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>64.28</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-0.71</v>
+        <v>-1.24</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>0.41</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-2.97</v>
+        <v>-3.49</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-2.94</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>71.59999999999999</v>
+        <v>61.34</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>88.75</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>8.699999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>9.19</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>11.98</v>
+        <v>11.84</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.02</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>84.23</v>
+        <v>81.66</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>84</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:22.57&lt;=25</t>
+          <t>今日买报：us500:RS2:15.05&lt;=22;us30:RS3:16.4&lt;=25;ixic:RS2:35.1&lt;=38</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>-0.13</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>0.2</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>7.13</v>
+        <v>7.98</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>7.13</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.26</v>
+        <v>11.34</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.26</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>15.05</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>15.05</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>6.31</v>
+        <v>6.11</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>6.31</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>13.07</v>
+        <v>12.77</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>13.07</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>16.4</v>
+        <v>12.97</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>16.4</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>11.91</v>
+        <v>13.65</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>11.91</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.09</v>
+        <v>13.26</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.09</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>35.1</v>
+        <v>86.75</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>35.1</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>7.67</v>
+        <v>7.7</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>7.62</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>1.9</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>61.91</v>
+        <v>62.14</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>62.05</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>1.04</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>1.43</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>59.42</v>
+        <v>59.05</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>76.38</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-1.55</v>
+        <v>-1.65</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-1.75</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.33</v>
+        <v>5.22</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>5.4</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>65.12</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>64.29000000000001</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.24</v>
+        <v>-0.29</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.24</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-3.49</v>
+        <v>-2.44</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.49</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>61.34</v>
+        <v>65.77</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>61.34</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>8.82</v>
+        <v>9.02</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>8.56</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>12.15</v>
+        <v>12.36</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.84</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>82.77</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>81.66</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:15.05&lt;=22;us30:RS3:16.4&lt;=25;ixic:RS2:35.1&lt;=38</t>
+          <t>今日买报：us30:RS3:12.97&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="88" t="n">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="C25" s="88" t="n">
         <v>7.28</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="89" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="C26" s="89" t="n">
         <v>0.29</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="89" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="C27" s="89" t="n">
         <v>0.5</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>7.98</v>
+        <v>7.71</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>7.98</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>11.34</v>
+        <v>11.08</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>11.34</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>73.40000000000001</v>
+        <v>38.26</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>73.40000000000001</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>6.11</v>
+        <v>5.81</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>6.11</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.77</v>
+        <v>11.43</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.77</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>12.97</v>
+        <v>7.45</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>12.97</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>13.65</v>
+        <v>13.26</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>13.65</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>13.26</v>
+        <v>13.75</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>13.26</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>86.75</v>
+        <v>54.06</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>86.75</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>10.43</v>
+        <v>10.07</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>7.7</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>3.03</v>
+        <v>2.69</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>2.01</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>71.66</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>62.14</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-0.18</v>
+        <v>-0.31</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>0.31</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>0.98</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>59.39</v>
+        <v>50.9</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>59.05</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>60.44</v>
+        <v>60.52</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>64.43000000000001</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.12</v>
+        <v>-2.55</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-0.29</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-1.02</v>
+        <v>-1.46</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-2.44</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>70.34</v>
+        <v>64.97</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>65.77</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>7.55</v>
+        <v>7.49</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>9.02</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>12.23</v>
+        <v>12.17</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>12.36</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>85.09</v>
+        <v>84.77</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>83.90000000000001</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="91" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:12.97&lt;=25</t>
+          <t>今日买报：us30:RS3:7.45&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.04</v>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>7.71</v>
+        <v>5.91</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>7.71</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>11.08</v>
+        <v>10.64</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>11.08</v>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>38.26</v>
+        <v>38.09</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>38.26</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>5.81</v>
+        <v>4.29</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>5.81</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>11.43</v>
+        <v>12.06</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>11.43</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>7.45</v>
+        <v>6.04</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>7.45</v>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>13.26</v>
+        <v>10.62</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>13.26</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>13.75</v>
+        <v>12.47</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>13.75</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>54.06</v>
+        <v>59.57</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>54.06</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-0.31</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>0.48</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>29.64</v>
+        <v>30.75</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>50.9</v>
@@ -10511,9 +10511,9 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C38" s="91" t="inlineStr">
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-1.35</v>
+        <v>-1.14</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-2.05</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.97</v>
+        <v>6.2</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>5.28</v>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>66.87</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>60.52</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-0.91</v>
+        <v>-1.21</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.55</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-0.64</v>
+        <v>-0.93</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-1.46</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>67.17</v>
+        <v>60.7</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>64.97</v>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>7.49</v>
+        <v>9.01</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>7.49</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>12.17</v>
+        <v>11.9</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>12.17</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>84.77</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>84.77</v>
@@ -11846,7 +11846,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:7.45&lt;=25</t>
+          <t>今日买报：us30:RS3:6.04&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.62</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.91</v>
+        <v>6.52</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.91</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.64</v>
+        <v>10.88</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.64</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>38.09</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>38.09</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>4.29</v>
+        <v>3.93</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>4.29</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.06</v>
+        <v>11.73</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.06</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>6.04</v>
+        <v>4.42</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>6.04</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-1.42</v>
+        <v>-1.45</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-1.14</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>6.2</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>62.36</v>
+        <v>62.08</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>68.18000000000001</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-1.21</v>
+        <v>-2.01</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-1.21</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-0.93</v>
+        <v>-2.7</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-0.93</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>60.7</v>
+        <v>44.02</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>60.7</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>8.25</v>
+        <v>7.78</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>9.01</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>11.54</v>
+        <v>11.06</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.9</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>79.86</v>
+        <v>64.64</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>80.84999999999999</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:6.04&lt;=25</t>
+          <t>今日买报：us30:RS3:4.42&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.16</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.9</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>6.52</v>
+        <v>5.81</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>6.52</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.88</v>
+        <v>10.35</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.88</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>73.43000000000001</v>
+        <v>33.91</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>73.43000000000001</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>3.93</v>
+        <v>3.15</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>3.93</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>11.73</v>
+        <v>10.94</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>11.73</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>4.42</v>
+        <v>2.24</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>4.42</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>12.4</v>
+        <v>11.88</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>12.4</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>13.3</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>88.39</v>
+        <v>64.33</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>88.39</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>4.87</v>
+        <v>4.35</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>6.2</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>0.55</v>
+        <v>0.06</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-0.53</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>60.77</v>
+        <v>55.97</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>58.68</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-2.98</v>
+        <v>-3.01</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-1.45</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.73</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>48.9</v>
+        <v>48.68</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>62.08</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-3.71</v>
+        <v>-3.13</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.01</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-2.87</v>
+        <v>-2.29</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-2.7</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>35.73</v>
+        <v>47.01</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>44.02</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>6.87</v>
+        <v>6.58</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>7.78</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>11.77</v>
+        <v>11.46</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.06</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>62.72</v>
+        <v>54.96</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>64.64</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:4.42&lt;=25</t>
+          <t>今日买报：us30:RS3:2.24&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.29</v>
+        <v>7.32</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.29</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.06</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.76</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.81</v>
+        <v>2.43</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.81</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.35</v>
+        <v>7.54</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.35</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>33.91</v>
+        <v>3.69</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>33.91</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>3.15</v>
+        <v>0.28</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>3.15</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>10.94</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>10.94</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>2.24</v>
+        <v>0.55</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>2.24</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>11.88</v>
+        <v>7.29</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>11.88</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>12.6</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>12.6</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>64.33</v>
+        <v>9.17</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>64.33</v>
@@ -9633,9 +9633,9 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B30" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C30" s="92" t="inlineStr">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>4.35</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-0.57</v>
+        <v>-1.27</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>0.06</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>55.76</v>
+        <v>48.31</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>55.97</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-5.14</v>
+        <v>-5.16</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-3.01</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>2.56</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>43.84</v>
+        <v>43.73</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>48.68</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.55</v>
+        <v>-2.39</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-3.13</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-3.4</v>
+        <v>-3.24</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-2.29</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>49.6</v>
+        <v>53.78</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>47.01</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>6.58</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>10.48</v>
+        <v>10.17</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>11.46</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>60.57</v>
+        <v>54.41</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>54.96</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:2.24&lt;=25</t>
+          <t>今日买报：us500:RS2:3.69&lt;=22;us30:RS3:0.55&lt;=25;ixic:RS2:9.17&lt;=38</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.5</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.03</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>2.43</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>7.54</v>
+        <v>7.16</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>7.54</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>3.69</v>
+        <v>3.51</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>3.69</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>0.28</v>
+        <v>1.02</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>0.28</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>8.199999999999999</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>0.55</v>
+        <v>2.07</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>0.55</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>7.29</v>
+        <v>7.14</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>7.29</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>9.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>9.359999999999999</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>9.17</v>
+        <v>8.75</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>9.17</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>1.34</v>
+        <v>2.49</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>3.01</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-3.16</v>
+        <v>-2.06</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-1.27</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>34.94</v>
+        <v>42.16</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>48.31</v>
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>35.93</v>
+        <v>35.94</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>43.73</v>
@@ -10973,9 +10973,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.39</v>
+        <v>-5.78</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.39</v>
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-3.24</v>
+        <v>-5.22</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-3.24</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>53.78</v>
+        <v>30.52</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>53.78</v>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>4.28</v>
+        <v>3.8</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>7</v>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>8.73</v>
+        <v>8.23</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>10.17</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>34.59</v>
+        <v>29.2</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>54.41</v>
@@ -11866,7 +11866,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:3.69&lt;=22;us30:RS3:0.55&lt;=25;ixic:RS2:9.17&lt;=38;vn:RS3:22.12&lt;=25;sensex:RS10:35.93&lt;=39</t>
+          <t>今日买报：us500:RS2:3.51&lt;=22;us30:RS3:2.07&lt;=25;ixic:RS2:8.75&lt;=38;vn:RS3:22.12&lt;=25;sensex:RS10:35.94&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>-100</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>4.82</v>
+        <v>5.76</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>4.82</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>8.49</v>
+        <v>8.34</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>8.49</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>89.12</v>
+        <v>85.53</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>89.12</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>2.28</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>9.960000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>9.960000000000001</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>69.41</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>69.41</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>10.13</v>
+        <v>11.78</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>10.13</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>9.15</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>9.15</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>89.31</v>
+        <v>85.38</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>89.31</v>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>3.9</v>
+        <v>4.65</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>1.24</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-3.67</v>
+        <v>-2.97</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-4.36</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>55.5</v>
+        <v>61.28</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>51.56</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-1.07</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-1.57</v>
+        <v>-1.61</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-0.74</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>76.67</v>
+        <v>74.3</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>80.23</v>
@@ -11877,7 +11877,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:13.23&gt;=10;sh:RS3:71.25&gt;=66;kc:RNG60:48.17&gt;=25;kc:RNG120:46.9&gt;=30;kc:RS5:72.27&gt;=65;cy:RNG60:28.92&gt;=25;us500:RS2:89.12&gt;=85</t>
+          <t>今日卖报：sh:RNG60:13.23&gt;=10;sh:RS3:71.25&gt;=66;kc:RNG60:48.17&gt;=25;kc:RNG120:46.9&gt;=30;kc:RS5:72.27&gt;=65;cy:RNG60:28.92&gt;=25;us500:RS2:85.53&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.04</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.73</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>4.58</v>
+        <v>3.63</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>4.58</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>7.06</v>
+        <v>4.85</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>7.06</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>26.76</v>
+        <v>11.56</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>26.76</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>1.89</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>9.42</v>
+        <v>7.18</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>9.42</v>
@@ -9083,13 +9083,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>40.35</v>
+        <v>22.32</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>40.35</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>10.02</v>
+        <v>8.75</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>10.02</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>7.01</v>
+        <v>4.5</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>7.01</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>24.8</v>
+        <v>11.7</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>24.8</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-7.19</v>
+        <v>-7.14</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-6.64</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-2.19</v>
+        <v>-2.14</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-1.62</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>33.69</v>
+        <v>34</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>37.69</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="91" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-1.83</v>
+        <v>-2.2</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-2.93</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-3.75</v>
+        <v>-4.11</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-2.88</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>54.66</v>
+        <v>46.49</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>60.14</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>4.01</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>8.08</v>
+        <v>8.16</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>9.59</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>34.92</v>
+        <v>35.85</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>41.58</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:24.8&lt;=38;sensex:RS10:33.69&lt;=39</t>
+          <t>今日买报：us500:RS2:11.56&lt;=22;us30:RS3:22.32&lt;=25;ixic:RS2:11.7&lt;=38;sensex:RS10:34.0&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.4</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>8.75</v>
+        <v>6.47</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>8.75</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>4.5</v>
+        <v>5.62</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>4.5</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>11.7</v>
+        <v>6.54</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>11.7</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="94" t="n">
-        <v>-0.03</v>
+        <v>-0.41</v>
       </c>
       <c r="C35" s="94" t="n">
         <v>0.16</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="94" t="n">
-        <v>-0.72</v>
+        <v>-1.09</v>
       </c>
       <c r="C36" s="94" t="n">
         <v>-0.92</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="B37" s="94" t="n">
-        <v>54.67</v>
+        <v>34.51</v>
       </c>
       <c r="C37" s="94" t="n">
         <v>57.76</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-5.15</v>
+        <v>-5.28</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-7.14</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>-2.62</v>
+        <v>-2.75</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>-2.14</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>34.02</v>
+        <v>33.12</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>34</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="93" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>-2.93</v>
+        <v>-2.13</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>-2.2</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-5.23</v>
+        <v>-4.45</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-4.11</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>48.86</v>
+        <v>63.25</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>46.49</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-16.02&lt;=-10;us500:RS2:11.56&lt;=22;us30:RS3:22.32&lt;=25;ixic:RS2:11.7&lt;=38;sensex:RS10:34.02&lt;=39</t>
+          <t>今日买报：cy:RNG60:-16.02&lt;=-10;us500:RS2:11.56&lt;=22;us30:RS3:22.32&lt;=25;ixic:RS2:6.54&lt;=38;sensex:RS10:33.12&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2412.xlsx
+++ b/report_2412.xlsx
@@ -6342,152 +6342,152 @@
       </c>
       <c r="B1" s="77" t="inlineStr">
         <is>
+          <t>250101</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
           <t>241231</t>
         </is>
       </c>
-      <c r="C1" s="77" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>241230</t>
         </is>
       </c>
-      <c r="D1" s="77" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>241229</t>
         </is>
       </c>
-      <c r="E1" s="77" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>241227</t>
         </is>
       </c>
-      <c r="F1" s="77" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>241226</t>
         </is>
       </c>
-      <c r="G1" s="77" t="inlineStr">
+      <c r="H1" s="77" t="inlineStr">
         <is>
           <t>241225</t>
         </is>
       </c>
-      <c r="H1" s="77" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>241224</t>
         </is>
       </c>
-      <c r="I1" s="77" t="inlineStr">
+      <c r="J1" s="77" t="inlineStr">
         <is>
           <t>241223</t>
         </is>
       </c>
-      <c r="J1" s="77" t="inlineStr">
+      <c r="K1" s="77" t="inlineStr">
         <is>
           <t>241222</t>
         </is>
       </c>
-      <c r="K1" s="77" t="inlineStr">
+      <c r="L1" s="77" t="inlineStr">
         <is>
           <t>241220</t>
         </is>
       </c>
-      <c r="L1" s="77" t="inlineStr">
+      <c r="M1" s="77" t="inlineStr">
         <is>
           <t>241219</t>
         </is>
       </c>
-      <c r="M1" s="77" t="inlineStr">
+      <c r="N1" s="77" t="inlineStr">
         <is>
           <t>241218</t>
         </is>
       </c>
-      <c r="N1" s="77" t="inlineStr">
+      <c r="O1" s="77" t="inlineStr">
         <is>
           <t>241217</t>
         </is>
       </c>
-      <c r="O1" s="77" t="inlineStr">
+      <c r="P1" s="77" t="inlineStr">
         <is>
           <t>241216</t>
         </is>
       </c>
-      <c r="P1" s="77" t="inlineStr">
+      <c r="Q1" s="77" t="inlineStr">
         <is>
           <t>241215</t>
         </is>
       </c>
-      <c r="Q1" s="77" t="inlineStr">
+      <c r="R1" s="77" t="inlineStr">
         <is>
           <t>241213</t>
         </is>
       </c>
-      <c r="R1" s="77" t="inlineStr">
+      <c r="S1" s="77" t="inlineStr">
         <is>
           <t>241212</t>
         </is>
       </c>
-      <c r="S1" s="77" t="inlineStr">
+      <c r="T1" s="77" t="inlineStr">
         <is>
           <t>241211</t>
         </is>
       </c>
-      <c r="T1" s="77" t="inlineStr">
+      <c r="U1" s="77" t="inlineStr">
         <is>
           <t>241210</t>
         </is>
       </c>
-      <c r="U1" s="77" t="inlineStr">
+      <c r="V1" s="77" t="inlineStr">
         <is>
           <t>241209</t>
         </is>
       </c>
-      <c r="V1" s="77" t="inlineStr">
+      <c r="W1" s="77" t="inlineStr">
         <is>
           <t>241208</t>
         </is>
       </c>
-      <c r="W1" s="77" t="inlineStr">
+      <c r="X1" s="77" t="inlineStr">
         <is>
           <t>241206</t>
         </is>
       </c>
-      <c r="X1" s="77" t="inlineStr">
+      <c r="Y1" s="77" t="inlineStr">
         <is>
           <t>241205</t>
         </is>
       </c>
-      <c r="Y1" s="77" t="inlineStr">
+      <c r="Z1" s="77" t="inlineStr">
         <is>
           <t>241204</t>
         </is>
       </c>
-      <c r="Z1" s="77" t="inlineStr">
+      <c r="AA1" s="77" t="inlineStr">
         <is>
           <t>241203</t>
         </is>
       </c>
-      <c r="AA1" s="77" t="inlineStr">
+      <c r="AB1" s="77" t="inlineStr">
         <is>
           <t>241202</t>
         </is>
       </c>
-      <c r="AB1" s="77" t="inlineStr">
+      <c r="AC1" s="77" t="inlineStr">
         <is>
           <t>241201</t>
         </is>
       </c>
-      <c r="AC1" s="77" t="inlineStr">
+      <c r="AD1" s="77" t="inlineStr">
         <is>
           <t>241129</t>
         </is>
       </c>
-      <c r="AD1" s="77" t="inlineStr">
+      <c r="AE1" s="77" t="inlineStr">
         <is>
           <t>241128</t>
-        </is>
-      </c>
-      <c r="AE1" s="77" t="inlineStr">
-        <is>
-          <t>241127</t>
         </is>
       </c>
     </row>
@@ -6502,144 +6502,144 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C2" s="92" t="inlineStr">
+      <c r="C2" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D2" s="92" t="inlineStr">
+      <c r="E2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E2" s="92" t="inlineStr">
+      <c r="F2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F2" s="92" t="inlineStr">
+      <c r="G2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="H2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="I2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I2" s="91" t="inlineStr">
+      <c r="J2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J2" s="91" t="inlineStr">
+      <c r="K2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K2" s="91" t="inlineStr">
+      <c r="L2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L2" s="91" t="inlineStr">
+      <c r="M2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="91" t="inlineStr">
+      <c r="N2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="91" t="inlineStr">
+      <c r="O2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O2" s="91" t="inlineStr">
+      <c r="P2" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q2" s="93" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="92" t="inlineStr">
+      <c r="S2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="T2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="U2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U2" s="92" t="inlineStr">
+      <c r="V2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V2" s="92" t="inlineStr">
+      <c r="W2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W2" s="92" t="inlineStr">
+      <c r="X2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X2" s="92" t="inlineStr">
+      <c r="Y2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y2" s="92" t="inlineStr">
+      <c r="Z2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z2" s="92" t="inlineStr">
+      <c r="AA2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA2" s="92" t="inlineStr">
+      <c r="AB2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB2" s="92" t="inlineStr">
+      <c r="AC2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC2" s="92" t="inlineStr">
+      <c r="AD2" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD2" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE2" s="93" t="inlineStr">
@@ -6658,91 +6658,91 @@
         <v>-3.95</v>
       </c>
       <c r="C3" s="94" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="D3" s="94" t="n">
         <v>2.12</v>
-      </c>
-      <c r="D3" s="94" t="n">
-        <v>10.12</v>
       </c>
       <c r="E3" s="94" t="n">
         <v>10.12</v>
       </c>
       <c r="F3" s="94" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="G3" s="94" t="n">
         <v>13.23</v>
       </c>
-      <c r="G3" s="94" t="n">
+      <c r="H3" s="94" t="n">
         <v>17.16</v>
       </c>
-      <c r="H3" s="94" t="n">
+      <c r="I3" s="94" t="n">
         <v>18.53</v>
       </c>
-      <c r="I3" s="94" t="n">
+      <c r="J3" s="94" t="n">
         <v>21.91</v>
-      </c>
-      <c r="J3" s="94" t="n">
-        <v>23.07</v>
       </c>
       <c r="K3" s="94" t="n">
         <v>23.07</v>
       </c>
       <c r="L3" s="94" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="M3" s="94" t="n">
         <v>23.17</v>
       </c>
-      <c r="M3" s="94" t="n">
+      <c r="N3" s="94" t="n">
         <v>24.47</v>
       </c>
-      <c r="N3" s="94" t="n">
+      <c r="O3" s="94" t="n">
         <v>24.31</v>
       </c>
-      <c r="O3" s="94" t="n">
+      <c r="P3" s="94" t="n">
         <v>24.63</v>
-      </c>
-      <c r="P3" s="94" t="n">
-        <v>24.62</v>
       </c>
       <c r="Q3" s="94" t="n">
         <v>24.62</v>
       </c>
       <c r="R3" s="94" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="S3" s="94" t="n">
         <v>26.14</v>
       </c>
-      <c r="S3" s="94" t="n">
+      <c r="T3" s="94" t="n">
         <v>25.43</v>
       </c>
-      <c r="T3" s="94" t="n">
+      <c r="U3" s="94" t="n">
         <v>23.75</v>
       </c>
-      <c r="U3" s="94" t="n">
+      <c r="V3" s="94" t="n">
         <v>22.03</v>
-      </c>
-      <c r="V3" s="94" t="n">
-        <v>22.26</v>
       </c>
       <c r="W3" s="94" t="n">
         <v>22.26</v>
       </c>
       <c r="X3" s="94" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="Y3" s="94" t="n">
         <v>20.19</v>
       </c>
-      <c r="Y3" s="94" t="n">
+      <c r="Z3" s="94" t="n">
         <v>19.69</v>
       </c>
-      <c r="Z3" s="94" t="n">
+      <c r="AA3" s="94" t="n">
         <v>18.88</v>
       </c>
-      <c r="AA3" s="94" t="n">
+      <c r="AB3" s="94" t="n">
         <v>19.16</v>
-      </c>
-      <c r="AB3" s="94" t="n">
-        <v>17.23</v>
       </c>
       <c r="AC3" s="94" t="n">
         <v>17.23</v>
       </c>
       <c r="AD3" s="94" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="AE3" s="94" t="n">
         <v>15.69</v>
-      </c>
-      <c r="AE3" s="94" t="n">
-        <v>15.91</v>
       </c>
     </row>
     <row r="4">
@@ -6755,91 +6755,91 @@
         <v>13.62</v>
       </c>
       <c r="C4" s="94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="D4" s="94" t="n">
         <v>15.21</v>
-      </c>
-      <c r="D4" s="94" t="n">
-        <v>14.01</v>
       </c>
       <c r="E4" s="94" t="n">
         <v>14.01</v>
       </c>
       <c r="F4" s="94" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="G4" s="94" t="n">
         <v>13.38</v>
       </c>
-      <c r="G4" s="94" t="n">
+      <c r="H4" s="94" t="n">
         <v>13.31</v>
       </c>
-      <c r="H4" s="94" t="n">
+      <c r="I4" s="94" t="n">
         <v>14.36</v>
       </c>
-      <c r="I4" s="94" t="n">
+      <c r="J4" s="94" t="n">
         <v>13.76</v>
-      </c>
-      <c r="J4" s="94" t="n">
-        <v>13.31</v>
       </c>
       <c r="K4" s="94" t="n">
         <v>13.31</v>
       </c>
       <c r="L4" s="94" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="M4" s="94" t="n">
         <v>14.24</v>
       </c>
-      <c r="M4" s="94" t="n">
+      <c r="N4" s="94" t="n">
         <v>14.14</v>
       </c>
-      <c r="N4" s="94" t="n">
+      <c r="O4" s="94" t="n">
         <v>12.12</v>
       </c>
-      <c r="O4" s="94" t="n">
+      <c r="P4" s="94" t="n">
         <v>12.67</v>
-      </c>
-      <c r="P4" s="94" t="n">
-        <v>12.39</v>
       </c>
       <c r="Q4" s="94" t="n">
         <v>12.39</v>
       </c>
       <c r="R4" s="94" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="S4" s="94" t="n">
         <v>14.23</v>
       </c>
-      <c r="S4" s="94" t="n">
+      <c r="T4" s="94" t="n">
         <v>13.81</v>
       </c>
-      <c r="T4" s="94" t="n">
+      <c r="U4" s="94" t="n">
         <v>12.86</v>
       </c>
-      <c r="U4" s="94" t="n">
+      <c r="V4" s="94" t="n">
         <v>12.33</v>
-      </c>
-      <c r="V4" s="94" t="n">
-        <v>12.07</v>
       </c>
       <c r="W4" s="94" t="n">
         <v>12.07</v>
       </c>
       <c r="X4" s="94" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="Y4" s="94" t="n">
         <v>11.26</v>
       </c>
-      <c r="Y4" s="94" t="n">
+      <c r="Z4" s="94" t="n">
         <v>10.27</v>
       </c>
-      <c r="Z4" s="94" t="n">
+      <c r="AA4" s="94" t="n">
         <v>10.82</v>
       </c>
-      <c r="AA4" s="94" t="n">
+      <c r="AB4" s="94" t="n">
         <v>9.74</v>
-      </c>
-      <c r="AB4" s="94" t="n">
-        <v>7.61</v>
       </c>
       <c r="AC4" s="94" t="n">
         <v>7.61</v>
       </c>
       <c r="AD4" s="94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AE4" s="94" t="n">
         <v>7.06</v>
-      </c>
-      <c r="AE4" s="94" t="n">
-        <v>7.22</v>
       </c>
     </row>
     <row r="5">
@@ -6852,91 +6852,91 @@
         <v>18.7</v>
       </c>
       <c r="C5" s="94" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D5" s="94" t="n">
         <v>81.11</v>
-      </c>
-      <c r="D5" s="94" t="n">
-        <v>73.47</v>
       </c>
       <c r="E5" s="94" t="n">
         <v>73.47</v>
       </c>
       <c r="F5" s="94" t="n">
+        <v>73.47</v>
+      </c>
+      <c r="G5" s="94" t="n">
         <v>71.25</v>
       </c>
-      <c r="G5" s="94" t="n">
+      <c r="H5" s="94" t="n">
         <v>67.02</v>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="I5" s="94" t="n">
         <v>67.27</v>
       </c>
-      <c r="I5" s="94" t="n">
+      <c r="J5" s="94" t="n">
         <v>20.98</v>
-      </c>
-      <c r="J5" s="94" t="n">
-        <v>33.57</v>
       </c>
       <c r="K5" s="94" t="n">
         <v>33.57</v>
       </c>
       <c r="L5" s="94" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="M5" s="94" t="n">
         <v>35.21</v>
       </c>
-      <c r="M5" s="94" t="n">
+      <c r="N5" s="94" t="n">
         <v>44.17</v>
       </c>
-      <c r="N5" s="94" t="n">
+      <c r="O5" s="94" t="n">
         <v>21.55</v>
       </c>
-      <c r="O5" s="94" t="n">
+      <c r="P5" s="94" t="n">
         <v>31.87</v>
-      </c>
-      <c r="P5" s="94" t="n">
-        <v>34.31</v>
       </c>
       <c r="Q5" s="94" t="n">
         <v>34.31</v>
       </c>
       <c r="R5" s="94" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="S5" s="94" t="n">
         <v>95.88</v>
       </c>
-      <c r="S5" s="94" t="n">
+      <c r="T5" s="94" t="n">
         <v>91.78</v>
       </c>
-      <c r="T5" s="94" t="n">
+      <c r="U5" s="94" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="U5" s="94" t="n">
+      <c r="V5" s="94" t="n">
         <v>82.47</v>
-      </c>
-      <c r="V5" s="94" t="n">
-        <v>85.33</v>
       </c>
       <c r="W5" s="94" t="n">
         <v>85.33</v>
       </c>
       <c r="X5" s="94" t="n">
+        <v>85.33</v>
+      </c>
+      <c r="Y5" s="94" t="n">
         <v>69.06999999999999</v>
       </c>
-      <c r="Y5" s="94" t="n">
+      <c r="Z5" s="94" t="n">
         <v>66.08</v>
       </c>
-      <c r="Z5" s="94" t="n">
+      <c r="AA5" s="94" t="n">
         <v>84.41</v>
       </c>
-      <c r="AA5" s="94" t="n">
+      <c r="AB5" s="94" t="n">
         <v>80.66</v>
-      </c>
-      <c r="AB5" s="94" t="n">
-        <v>67.48999999999999</v>
       </c>
       <c r="AC5" s="94" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="AD5" s="94" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="AE5" s="94" t="n">
         <v>48.2</v>
-      </c>
-      <c r="AE5" s="94" t="n">
-        <v>58.86</v>
       </c>
     </row>
     <row r="6">
@@ -6950,144 +6950,144 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D6" s="92" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E6" s="92" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
+      <c r="G6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G6" s="92" t="inlineStr">
+      <c r="H6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H6" s="92" t="inlineStr">
+      <c r="I6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="J6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="K6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L6" s="92" t="inlineStr">
+      <c r="M6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="N6" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N6" s="91" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O6" s="91" t="inlineStr">
+      <c r="P6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P6" s="91" t="inlineStr">
+      <c r="Q6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q6" s="91" t="inlineStr">
+      <c r="R6" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="S6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="T6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="U6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U6" s="92" t="inlineStr">
+      <c r="V6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V6" s="92" t="inlineStr">
+      <c r="W6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W6" s="92" t="inlineStr">
+      <c r="X6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X6" s="92" t="inlineStr">
+      <c r="Y6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y6" s="92" t="inlineStr">
+      <c r="Z6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z6" s="92" t="inlineStr">
+      <c r="AA6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA6" s="92" t="inlineStr">
+      <c r="AB6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB6" s="92" t="inlineStr">
+      <c r="AC6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC6" s="92" t="inlineStr">
+      <c r="AD6" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD6" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE6" s="93" t="inlineStr">
@@ -7106,91 +7106,91 @@
         <v>-3.42</v>
       </c>
       <c r="C7" s="94" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="D7" s="94" t="n">
         <v>17</v>
-      </c>
-      <c r="D7" s="94" t="n">
-        <v>37.64</v>
       </c>
       <c r="E7" s="94" t="n">
         <v>37.64</v>
       </c>
       <c r="F7" s="94" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="G7" s="94" t="n">
         <v>48.17</v>
       </c>
-      <c r="G7" s="94" t="n">
+      <c r="H7" s="94" t="n">
         <v>52.45</v>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="I7" s="94" t="n">
         <v>52.02</v>
       </c>
-      <c r="I7" s="94" t="n">
+      <c r="J7" s="94" t="n">
         <v>55.3</v>
-      </c>
-      <c r="J7" s="94" t="n">
-        <v>55.96</v>
       </c>
       <c r="K7" s="94" t="n">
         <v>55.96</v>
       </c>
       <c r="L7" s="94" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="M7" s="94" t="n">
         <v>52.42</v>
       </c>
-      <c r="M7" s="94" t="n">
+      <c r="N7" s="94" t="n">
         <v>51.61</v>
       </c>
-      <c r="N7" s="94" t="n">
+      <c r="O7" s="94" t="n">
         <v>47.67</v>
       </c>
-      <c r="O7" s="94" t="n">
+      <c r="P7" s="94" t="n">
         <v>48.03</v>
-      </c>
-      <c r="P7" s="94" t="n">
-        <v>48.99</v>
       </c>
       <c r="Q7" s="94" t="n">
         <v>48.99</v>
       </c>
       <c r="R7" s="94" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="S7" s="94" t="n">
         <v>53.16</v>
       </c>
-      <c r="S7" s="94" t="n">
+      <c r="T7" s="94" t="n">
         <v>53.78</v>
       </c>
-      <c r="T7" s="94" t="n">
+      <c r="U7" s="94" t="n">
         <v>52.63</v>
       </c>
-      <c r="U7" s="94" t="n">
+      <c r="V7" s="94" t="n">
         <v>49.48</v>
-      </c>
-      <c r="V7" s="94" t="n">
-        <v>50.9</v>
       </c>
       <c r="W7" s="94" t="n">
         <v>50.9</v>
       </c>
       <c r="X7" s="94" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Y7" s="94" t="n">
         <v>48.43</v>
       </c>
-      <c r="Y7" s="94" t="n">
+      <c r="Z7" s="94" t="n">
         <v>49.16</v>
       </c>
-      <c r="Z7" s="94" t="n">
+      <c r="AA7" s="94" t="n">
         <v>44.82</v>
       </c>
-      <c r="AA7" s="94" t="n">
+      <c r="AB7" s="94" t="n">
         <v>49.47</v>
-      </c>
-      <c r="AB7" s="94" t="n">
-        <v>50.08</v>
       </c>
       <c r="AC7" s="94" t="n">
         <v>50.08</v>
       </c>
       <c r="AD7" s="94" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AE7" s="94" t="n">
         <v>45.87</v>
-      </c>
-      <c r="AE7" s="94" t="n">
-        <v>44.46</v>
       </c>
     </row>
     <row r="8">
@@ -7203,91 +7203,91 @@
         <v>41.51</v>
       </c>
       <c r="C8" s="94" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="D8" s="94" t="n">
         <v>47.84</v>
-      </c>
-      <c r="D8" s="94" t="n">
-        <v>45.14</v>
       </c>
       <c r="E8" s="94" t="n">
         <v>45.14</v>
       </c>
       <c r="F8" s="94" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="G8" s="94" t="n">
         <v>46.9</v>
       </c>
-      <c r="G8" s="94" t="n">
+      <c r="H8" s="94" t="n">
         <v>43.37</v>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="I8" s="94" t="n">
         <v>42.4</v>
       </c>
-      <c r="I8" s="94" t="n">
+      <c r="J8" s="94" t="n">
         <v>39.6</v>
-      </c>
-      <c r="J8" s="94" t="n">
-        <v>38.59</v>
       </c>
       <c r="K8" s="94" t="n">
         <v>38.59</v>
       </c>
       <c r="L8" s="94" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="M8" s="94" t="n">
         <v>38.35</v>
       </c>
-      <c r="M8" s="94" t="n">
+      <c r="N8" s="94" t="n">
         <v>32.79</v>
       </c>
-      <c r="N8" s="94" t="n">
+      <c r="O8" s="94" t="n">
         <v>27.55</v>
       </c>
-      <c r="O8" s="94" t="n">
+      <c r="P8" s="94" t="n">
         <v>29.15</v>
-      </c>
-      <c r="P8" s="94" t="n">
-        <v>31.67</v>
       </c>
       <c r="Q8" s="94" t="n">
         <v>31.67</v>
       </c>
       <c r="R8" s="94" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="S8" s="94" t="n">
         <v>33.56</v>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="T8" s="94" t="n">
         <v>33.03</v>
       </c>
-      <c r="T8" s="94" t="n">
+      <c r="U8" s="94" t="n">
         <v>34.03</v>
       </c>
-      <c r="U8" s="94" t="n">
+      <c r="V8" s="94" t="n">
         <v>32.2</v>
-      </c>
-      <c r="V8" s="94" t="n">
-        <v>34.38</v>
       </c>
       <c r="W8" s="94" t="n">
         <v>34.38</v>
       </c>
       <c r="X8" s="94" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="Y8" s="94" t="n">
         <v>32.55</v>
       </c>
-      <c r="Y8" s="94" t="n">
+      <c r="Z8" s="94" t="n">
         <v>35.43</v>
       </c>
-      <c r="Z8" s="94" t="n">
+      <c r="AA8" s="94" t="n">
         <v>35.26</v>
       </c>
-      <c r="AA8" s="94" t="n">
+      <c r="AB8" s="94" t="n">
         <v>35.07</v>
-      </c>
-      <c r="AB8" s="94" t="n">
-        <v>33.67</v>
       </c>
       <c r="AC8" s="94" t="n">
         <v>33.67</v>
       </c>
       <c r="AD8" s="94" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AE8" s="94" t="n">
         <v>31.08</v>
-      </c>
-      <c r="AE8" s="94" t="n">
-        <v>32.66</v>
       </c>
     </row>
     <row r="9">
@@ -7300,91 +7300,91 @@
         <v>32.85</v>
       </c>
       <c r="C9" s="94" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="D9" s="94" t="n">
         <v>62.46</v>
-      </c>
-      <c r="D9" s="94" t="n">
-        <v>60.63</v>
       </c>
       <c r="E9" s="94" t="n">
         <v>60.63</v>
       </c>
       <c r="F9" s="94" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="G9" s="94" t="n">
         <v>72.27</v>
       </c>
-      <c r="G9" s="94" t="n">
+      <c r="H9" s="94" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="I9" s="94" t="n">
         <v>64.23999999999999</v>
       </c>
-      <c r="I9" s="94" t="n">
+      <c r="J9" s="94" t="n">
         <v>53.48</v>
-      </c>
-      <c r="J9" s="94" t="n">
-        <v>66.59999999999999</v>
       </c>
       <c r="K9" s="94" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="L9" s="94" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="M9" s="94" t="n">
         <v>53.37</v>
       </c>
-      <c r="M9" s="94" t="n">
+      <c r="N9" s="94" t="n">
         <v>41.72</v>
       </c>
-      <c r="N9" s="94" t="n">
+      <c r="O9" s="94" t="n">
         <v>22.56</v>
       </c>
-      <c r="O9" s="94" t="n">
+      <c r="P9" s="94" t="n">
         <v>26.47</v>
-      </c>
-      <c r="P9" s="94" t="n">
-        <v>35.38</v>
       </c>
       <c r="Q9" s="94" t="n">
         <v>35.38</v>
       </c>
       <c r="R9" s="94" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="S9" s="94" t="n">
         <v>58.18</v>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="T9" s="94" t="n">
         <v>54.01</v>
       </c>
-      <c r="T9" s="94" t="n">
+      <c r="U9" s="94" t="n">
         <v>58.7</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="V9" s="94" t="n">
         <v>51.94</v>
-      </c>
-      <c r="V9" s="94" t="n">
-        <v>64.31</v>
       </c>
       <c r="W9" s="94" t="n">
         <v>64.31</v>
       </c>
       <c r="X9" s="94" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="Y9" s="94" t="n">
         <v>54.42</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="Z9" s="94" t="n">
         <v>52.35</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="AA9" s="94" t="n">
         <v>57.32</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="AB9" s="94" t="n">
         <v>66.31</v>
-      </c>
-      <c r="AB9" s="94" t="n">
-        <v>62.56</v>
       </c>
       <c r="AC9" s="94" t="n">
         <v>62.56</v>
       </c>
       <c r="AD9" s="94" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="AE9" s="94" t="n">
         <v>50</v>
-      </c>
-      <c r="AE9" s="94" t="n">
-        <v>51.33</v>
       </c>
     </row>
     <row r="10">
@@ -7398,144 +7398,144 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C10" s="93" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D10" s="93" t="inlineStr">
+      <c r="E10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E10" s="93" t="inlineStr">
+      <c r="F10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F10" s="93" t="inlineStr">
+      <c r="G10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G10" s="93" t="inlineStr">
+      <c r="H10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="93" t="inlineStr">
+      <c r="I10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="91" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J10" s="93" t="inlineStr">
+      <c r="K10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K10" s="93" t="inlineStr">
+      <c r="L10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L10" s="93" t="inlineStr">
+      <c r="M10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M10" s="91" t="inlineStr">
+      <c r="N10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N10" s="91" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O10" s="91" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P10" s="91" t="inlineStr">
+      <c r="Q10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q10" s="91" t="inlineStr">
+      <c r="R10" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="T10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="U10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V10" s="92" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W10" s="92" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="Y10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Z10" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z10" s="92" t="inlineStr">
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA10" s="92" t="inlineStr">
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB10" s="92" t="inlineStr">
+      <c r="AC10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC10" s="92" t="inlineStr">
+      <c r="AD10" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD10" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AE10" s="93" t="inlineStr">
@@ -7554,91 +7554,91 @@
         <v>-16.02</v>
       </c>
       <c r="C11" s="94" t="n">
+        <v>-16.02</v>
+      </c>
+      <c r="D11" s="94" t="n">
         <v>1.43</v>
-      </c>
-      <c r="D11" s="94" t="n">
-        <v>16.94</v>
       </c>
       <c r="E11" s="94" t="n">
         <v>16.94</v>
       </c>
       <c r="F11" s="94" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="G11" s="94" t="n">
         <v>28.92</v>
       </c>
-      <c r="G11" s="94" t="n">
+      <c r="H11" s="94" t="n">
         <v>34.1</v>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="I11" s="94" t="n">
         <v>37.03</v>
       </c>
-      <c r="I11" s="94" t="n">
+      <c r="J11" s="94" t="n">
         <v>42.95</v>
-      </c>
-      <c r="J11" s="94" t="n">
-        <v>43.8</v>
       </c>
       <c r="K11" s="94" t="n">
         <v>43.8</v>
       </c>
       <c r="L11" s="94" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="M11" s="94" t="n">
         <v>43.14</v>
       </c>
-      <c r="M11" s="94" t="n">
+      <c r="N11" s="94" t="n">
         <v>43.61</v>
       </c>
-      <c r="N11" s="94" t="n">
+      <c r="O11" s="94" t="n">
         <v>43.38</v>
       </c>
-      <c r="O11" s="94" t="n">
+      <c r="P11" s="94" t="n">
         <v>41.87</v>
-      </c>
-      <c r="P11" s="94" t="n">
-        <v>43.44</v>
       </c>
       <c r="Q11" s="94" t="n">
         <v>43.44</v>
       </c>
       <c r="R11" s="94" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="S11" s="94" t="n">
         <v>48.84</v>
       </c>
-      <c r="S11" s="94" t="n">
+      <c r="T11" s="94" t="n">
         <v>46.95</v>
       </c>
-      <c r="T11" s="94" t="n">
+      <c r="U11" s="94" t="n">
         <v>47.2</v>
       </c>
-      <c r="U11" s="94" t="n">
+      <c r="V11" s="94" t="n">
         <v>43.71</v>
-      </c>
-      <c r="V11" s="94" t="n">
-        <v>45.83</v>
       </c>
       <c r="W11" s="94" t="n">
         <v>45.83</v>
       </c>
       <c r="X11" s="94" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="Y11" s="94" t="n">
         <v>42.74</v>
       </c>
-      <c r="Y11" s="94" t="n">
+      <c r="Z11" s="94" t="n">
         <v>44.01</v>
       </c>
-      <c r="Z11" s="94" t="n">
+      <c r="AA11" s="94" t="n">
         <v>42.08</v>
       </c>
-      <c r="AA11" s="94" t="n">
+      <c r="AB11" s="94" t="n">
         <v>46.33</v>
-      </c>
-      <c r="AB11" s="94" t="n">
-        <v>45.22</v>
       </c>
       <c r="AC11" s="94" t="n">
         <v>45.22</v>
       </c>
       <c r="AD11" s="94" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="AE11" s="94" t="n">
         <v>41.75</v>
-      </c>
-      <c r="AE11" s="94" t="n">
-        <v>42.93</v>
       </c>
     </row>
     <row r="12">
@@ -7651,91 +7651,91 @@
         <v>29.36</v>
       </c>
       <c r="C12" s="94" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="D12" s="94" t="n">
         <v>33.94</v>
-      </c>
-      <c r="D12" s="94" t="n">
-        <v>32.82</v>
       </c>
       <c r="E12" s="94" t="n">
         <v>32.82</v>
       </c>
       <c r="F12" s="94" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="G12" s="94" t="n">
         <v>32.72</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="H12" s="94" t="n">
         <v>30.82</v>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="I12" s="94" t="n">
         <v>31.49</v>
       </c>
-      <c r="I12" s="94" t="n">
+      <c r="J12" s="94" t="n">
         <v>28.46</v>
-      </c>
-      <c r="J12" s="94" t="n">
-        <v>27.68</v>
       </c>
       <c r="K12" s="94" t="n">
         <v>27.68</v>
       </c>
       <c r="L12" s="94" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="M12" s="94" t="n">
         <v>30.21</v>
       </c>
-      <c r="M12" s="94" t="n">
+      <c r="N12" s="94" t="n">
         <v>27.18</v>
       </c>
-      <c r="N12" s="94" t="n">
+      <c r="O12" s="94" t="n">
         <v>25.36</v>
       </c>
-      <c r="O12" s="94" t="n">
+      <c r="P12" s="94" t="n">
         <v>24.9</v>
-      </c>
-      <c r="P12" s="94" t="n">
-        <v>24.98</v>
       </c>
       <c r="Q12" s="94" t="n">
         <v>24.98</v>
       </c>
       <c r="R12" s="94" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="S12" s="94" t="n">
         <v>26.54</v>
       </c>
-      <c r="S12" s="94" t="n">
+      <c r="T12" s="94" t="n">
         <v>25.21</v>
       </c>
-      <c r="T12" s="94" t="n">
+      <c r="U12" s="94" t="n">
         <v>26.39</v>
       </c>
-      <c r="U12" s="94" t="n">
+      <c r="V12" s="94" t="n">
         <v>26.48</v>
-      </c>
-      <c r="V12" s="94" t="n">
-        <v>27.4</v>
       </c>
       <c r="W12" s="94" t="n">
         <v>27.4</v>
       </c>
       <c r="X12" s="94" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Y12" s="94" t="n">
         <v>24.29</v>
       </c>
-      <c r="Y12" s="94" t="n">
+      <c r="Z12" s="94" t="n">
         <v>24.27</v>
       </c>
-      <c r="Z12" s="94" t="n">
+      <c r="AA12" s="94" t="n">
         <v>23.35</v>
       </c>
-      <c r="AA12" s="94" t="n">
+      <c r="AB12" s="94" t="n">
         <v>23.01</v>
-      </c>
-      <c r="AB12" s="94" t="n">
-        <v>20.63</v>
       </c>
       <c r="AC12" s="94" t="n">
         <v>20.63</v>
       </c>
       <c r="AD12" s="94" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="AE12" s="94" t="n">
         <v>19.26</v>
-      </c>
-      <c r="AE12" s="94" t="n">
-        <v>22.36</v>
       </c>
     </row>
     <row r="13">
@@ -7748,91 +7748,91 @@
         <v>9.470000000000001</v>
       </c>
       <c r="C13" s="94" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="D13" s="94" t="n">
         <v>49.72</v>
-      </c>
-      <c r="D13" s="94" t="n">
-        <v>46.46</v>
       </c>
       <c r="E13" s="94" t="n">
         <v>46.46</v>
       </c>
       <c r="F13" s="94" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="G13" s="94" t="n">
         <v>54.92</v>
       </c>
-      <c r="G13" s="94" t="n">
+      <c r="H13" s="94" t="n">
         <v>42.96</v>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="I13" s="94" t="n">
         <v>57.53</v>
       </c>
-      <c r="I13" s="94" t="n">
+      <c r="J13" s="94" t="n">
         <v>19.45</v>
-      </c>
-      <c r="J13" s="94" t="n">
-        <v>39.46</v>
       </c>
       <c r="K13" s="94" t="n">
         <v>39.46</v>
       </c>
       <c r="L13" s="94" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="M13" s="94" t="n">
         <v>44.97</v>
       </c>
-      <c r="M13" s="94" t="n">
+      <c r="N13" s="94" t="n">
         <v>24.25</v>
       </c>
-      <c r="N13" s="94" t="n">
+      <c r="O13" s="94" t="n">
         <v>22.62</v>
       </c>
-      <c r="O13" s="94" t="n">
+      <c r="P13" s="94" t="n">
         <v>22.73</v>
-      </c>
-      <c r="P13" s="94" t="n">
-        <v>34.39</v>
       </c>
       <c r="Q13" s="94" t="n">
         <v>34.39</v>
       </c>
       <c r="R13" s="94" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="S13" s="94" t="n">
         <v>81.18000000000001</v>
       </c>
-      <c r="S13" s="94" t="n">
+      <c r="T13" s="94" t="n">
         <v>63.29</v>
       </c>
-      <c r="T13" s="94" t="n">
+      <c r="U13" s="94" t="n">
         <v>66.7</v>
       </c>
-      <c r="U13" s="94" t="n">
+      <c r="V13" s="94" t="n">
         <v>57.05</v>
-      </c>
-      <c r="V13" s="94" t="n">
-        <v>74.19</v>
       </c>
       <c r="W13" s="94" t="n">
         <v>74.19</v>
       </c>
       <c r="X13" s="94" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="Y13" s="94" t="n">
         <v>48.84</v>
       </c>
-      <c r="Y13" s="94" t="n">
+      <c r="Z13" s="94" t="n">
         <v>42.15</v>
       </c>
-      <c r="Z13" s="94" t="n">
+      <c r="AA13" s="94" t="n">
         <v>64.58</v>
       </c>
-      <c r="AA13" s="94" t="n">
+      <c r="AB13" s="94" t="n">
         <v>72.61</v>
-      </c>
-      <c r="AB13" s="94" t="n">
-        <v>62.93</v>
       </c>
       <c r="AC13" s="94" t="n">
         <v>62.93</v>
       </c>
       <c r="AD13" s="94" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="AE13" s="94" t="n">
         <v>37.68</v>
-      </c>
-      <c r="AE13" s="94" t="n">
-        <v>55.95</v>
       </c>
     </row>
     <row r="14">
@@ -7881,94 +7881,94 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J14" s="91" t="inlineStr">
+      <c r="J14" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K14" s="91" t="inlineStr">
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L14" s="91" t="inlineStr">
+      <c r="M14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M14" s="91" t="inlineStr">
+      <c r="N14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N14" s="91" t="inlineStr">
+      <c r="O14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O14" s="91" t="inlineStr">
+      <c r="P14" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P14" s="93" t="inlineStr">
+      <c r="Q14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q14" s="93" t="inlineStr">
+      <c r="R14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R14" s="92" t="inlineStr">
+      <c r="S14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S14" s="93" t="inlineStr">
+      <c r="T14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T14" s="92" t="inlineStr">
+      <c r="U14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U14" s="92" t="inlineStr">
+      <c r="V14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V14" s="92" t="inlineStr">
+      <c r="W14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W14" s="92" t="inlineStr">
+      <c r="X14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="Y14" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y14" s="92" t="inlineStr">
+      <c r="Z14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="92" t="inlineStr">
+      <c r="AA14" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AA14" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AB14" s="93" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>-9.289999999999999</v>
       </c>
       <c r="C15" s="94" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="D15" s="94" t="n">
         <v>-10.7</v>
-      </c>
-      <c r="D15" s="94" t="n">
-        <v>-4.94</v>
       </c>
       <c r="E15" s="94" t="n">
         <v>-4.94</v>
       </c>
       <c r="F15" s="94" t="n">
-        <v>-2.59</v>
+        <v>-4.94</v>
       </c>
       <c r="G15" s="94" t="n">
         <v>-2.59</v>
@@ -8020,73 +8020,73 @@
         <v>-2.59</v>
       </c>
       <c r="I15" s="94" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="J15" s="94" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="J15" s="94" t="n">
-        <v>3.09</v>
       </c>
       <c r="K15" s="94" t="n">
         <v>3.09</v>
       </c>
       <c r="L15" s="94" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M15" s="94" t="n">
         <v>3.96</v>
       </c>
-      <c r="M15" s="94" t="n">
+      <c r="N15" s="94" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="N15" s="94" t="n">
+      <c r="O15" s="94" t="n">
         <v>7.9</v>
       </c>
-      <c r="O15" s="94" t="n">
+      <c r="P15" s="94" t="n">
         <v>9.890000000000001</v>
-      </c>
-      <c r="P15" s="94" t="n">
-        <v>13.09</v>
       </c>
       <c r="Q15" s="94" t="n">
         <v>13.09</v>
       </c>
       <c r="R15" s="94" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="S15" s="94" t="n">
         <v>17.08</v>
       </c>
-      <c r="S15" s="94" t="n">
+      <c r="T15" s="94" t="n">
         <v>16.04</v>
       </c>
-      <c r="T15" s="94" t="n">
+      <c r="U15" s="94" t="n">
         <v>17.81</v>
       </c>
-      <c r="U15" s="94" t="n">
+      <c r="V15" s="94" t="n">
         <v>19.32</v>
-      </c>
-      <c r="V15" s="94" t="n">
-        <v>15.27</v>
       </c>
       <c r="W15" s="94" t="n">
         <v>15.27</v>
       </c>
       <c r="X15" s="94" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="Y15" s="94" t="n">
         <v>13.74</v>
       </c>
-      <c r="Y15" s="94" t="n">
+      <c r="Z15" s="94" t="n">
         <v>13.17</v>
       </c>
-      <c r="Z15" s="94" t="n">
+      <c r="AA15" s="94" t="n">
         <v>13.11</v>
       </c>
-      <c r="AA15" s="94" t="n">
+      <c r="AB15" s="94" t="n">
         <v>10.76</v>
-      </c>
-      <c r="AB15" s="94" t="n">
-        <v>9.789999999999999</v>
       </c>
       <c r="AC15" s="94" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="AD15" s="94" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="AE15" s="94" t="n">
         <v>7.66</v>
-      </c>
-      <c r="AE15" s="94" t="n">
-        <v>10.21</v>
       </c>
     </row>
     <row r="16">
@@ -8099,16 +8099,16 @@
         <v>14.47</v>
       </c>
       <c r="C16" s="94" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="D16" s="94" t="n">
         <v>12.59</v>
-      </c>
-      <c r="D16" s="94" t="n">
-        <v>11.44</v>
       </c>
       <c r="E16" s="94" t="n">
         <v>11.44</v>
       </c>
       <c r="F16" s="94" t="n">
-        <v>11.79</v>
+        <v>11.44</v>
       </c>
       <c r="G16" s="94" t="n">
         <v>11.79</v>
@@ -8117,73 +8117,73 @@
         <v>11.79</v>
       </c>
       <c r="I16" s="94" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="J16" s="94" t="n">
         <v>11.9</v>
-      </c>
-      <c r="J16" s="94" t="n">
-        <v>11.3</v>
       </c>
       <c r="K16" s="94" t="n">
         <v>11.3</v>
       </c>
       <c r="L16" s="94" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M16" s="94" t="n">
         <v>11.49</v>
       </c>
-      <c r="M16" s="94" t="n">
+      <c r="N16" s="94" t="n">
         <v>9.81</v>
       </c>
-      <c r="N16" s="94" t="n">
+      <c r="O16" s="94" t="n">
         <v>9.01</v>
       </c>
-      <c r="O16" s="94" t="n">
+      <c r="P16" s="94" t="n">
         <v>9.81</v>
-      </c>
-      <c r="P16" s="94" t="n">
-        <v>10.78</v>
       </c>
       <c r="Q16" s="94" t="n">
         <v>10.78</v>
       </c>
       <c r="R16" s="94" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="S16" s="94" t="n">
         <v>11.24</v>
       </c>
-      <c r="S16" s="94" t="n">
+      <c r="T16" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="T16" s="94" t="n">
+      <c r="U16" s="94" t="n">
         <v>13.37</v>
       </c>
-      <c r="U16" s="94" t="n">
+      <c r="V16" s="94" t="n">
         <v>13.82</v>
-      </c>
-      <c r="V16" s="94" t="n">
-        <v>10.72</v>
       </c>
       <c r="W16" s="94" t="n">
         <v>10.72</v>
       </c>
       <c r="X16" s="94" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="Y16" s="94" t="n">
         <v>7.99</v>
       </c>
-      <c r="Y16" s="94" t="n">
+      <c r="Z16" s="94" t="n">
         <v>10.06</v>
       </c>
-      <c r="Z16" s="94" t="n">
+      <c r="AA16" s="94" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="AA16" s="94" t="n">
+      <c r="AB16" s="94" t="n">
         <v>6.44</v>
-      </c>
-      <c r="AB16" s="94" t="n">
-        <v>5.12</v>
       </c>
       <c r="AC16" s="94" t="n">
         <v>5.12</v>
       </c>
       <c r="AD16" s="94" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AE16" s="94" t="n">
         <v>5.11</v>
-      </c>
-      <c r="AE16" s="94" t="n">
-        <v>6.28</v>
       </c>
     </row>
     <row r="17">
@@ -8196,16 +8196,16 @@
         <v>62.48</v>
       </c>
       <c r="C17" s="94" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="D17" s="94" t="n">
         <v>60.29</v>
-      </c>
-      <c r="D17" s="94" t="n">
-        <v>68.20999999999999</v>
       </c>
       <c r="E17" s="94" t="n">
         <v>68.20999999999999</v>
       </c>
       <c r="F17" s="94" t="n">
-        <v>69.3</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="G17" s="94" t="n">
         <v>69.3</v>
@@ -8214,73 +8214,73 @@
         <v>69.3</v>
       </c>
       <c r="I17" s="94" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="J17" s="94" t="n">
         <v>54.21</v>
-      </c>
-      <c r="J17" s="94" t="n">
-        <v>36.55</v>
       </c>
       <c r="K17" s="94" t="n">
         <v>36.55</v>
       </c>
       <c r="L17" s="94" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="M17" s="94" t="n">
         <v>38.75</v>
       </c>
-      <c r="M17" s="94" t="n">
+      <c r="N17" s="94" t="n">
         <v>46.05</v>
       </c>
-      <c r="N17" s="94" t="n">
+      <c r="O17" s="94" t="n">
         <v>31.96</v>
       </c>
-      <c r="O17" s="94" t="n">
+      <c r="P17" s="94" t="n">
         <v>36.05</v>
-      </c>
-      <c r="P17" s="94" t="n">
-        <v>43.83</v>
       </c>
       <c r="Q17" s="94" t="n">
         <v>43.83</v>
       </c>
       <c r="R17" s="94" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="S17" s="94" t="n">
         <v>72.11</v>
       </c>
-      <c r="S17" s="94" t="n">
+      <c r="T17" s="94" t="n">
         <v>61.53</v>
       </c>
-      <c r="T17" s="94" t="n">
+      <c r="U17" s="94" t="n">
         <v>75.38</v>
       </c>
-      <c r="U17" s="94" t="n">
+      <c r="V17" s="94" t="n">
         <v>84.79000000000001</v>
-      </c>
-      <c r="V17" s="94" t="n">
-        <v>69.61</v>
       </c>
       <c r="W17" s="94" t="n">
         <v>69.61</v>
       </c>
       <c r="X17" s="94" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="Y17" s="94" t="n">
         <v>47.86</v>
       </c>
-      <c r="Y17" s="94" t="n">
+      <c r="Z17" s="94" t="n">
         <v>70.38</v>
       </c>
-      <c r="Z17" s="94" t="n">
+      <c r="AA17" s="94" t="n">
         <v>70.91</v>
       </c>
-      <c r="AA17" s="94" t="n">
+      <c r="AB17" s="94" t="n">
         <v>59.2</v>
-      </c>
-      <c r="AB17" s="94" t="n">
-        <v>49.3</v>
       </c>
       <c r="AC17" s="94" t="n">
         <v>49.3</v>
       </c>
       <c r="AD17" s="94" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AE17" s="94" t="n">
         <v>44.81</v>
-      </c>
-      <c r="AE17" s="94" t="n">
-        <v>61.96</v>
       </c>
     </row>
     <row r="18">
@@ -8309,135 +8309,133 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="F18" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G18" s="92" t="inlineStr">
+      <c r="H18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H18" s="92" t="inlineStr">
+      <c r="I18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I18" s="93" t="inlineStr">
+      <c r="J18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J18" s="93" t="inlineStr">
+      <c r="K18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K18" s="93" t="inlineStr">
+      <c r="L18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="M18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M18" s="91" t="inlineStr">
+      <c r="N18" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N18" s="93" t="inlineStr">
+      <c r="O18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O18" s="92" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="Q18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q18" s="93" t="inlineStr">
+      <c r="R18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R18" s="93" t="inlineStr">
+      <c r="S18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S18" s="92" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T18" s="93" t="inlineStr">
+      <c r="U18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U18" s="93" t="inlineStr">
+      <c r="V18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V18" s="93" t="inlineStr">
+      <c r="W18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W18" s="93" t="inlineStr">
+      <c r="X18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X18" s="93" t="inlineStr">
+      <c r="Y18" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y18" s="92" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z18" s="92" t="inlineStr">
+      <c r="AA18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA18" s="92" t="inlineStr">
+      <c r="AB18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB18" s="92" t="inlineStr">
+      <c r="AC18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC18" s="92" t="inlineStr">
+      <c r="AD18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE18" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -8447,94 +8445,94 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C19" s="94" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D19" s="94" t="n">
         <v>3.63</v>
-      </c>
-      <c r="C19" s="94" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="D19" s="94" t="n">
-        <v>4.58</v>
       </c>
       <c r="E19" s="94" t="n">
         <v>4.58</v>
       </c>
       <c r="F19" s="94" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="G19" s="94" t="n">
         <v>5.76</v>
-      </c>
-      <c r="G19" s="94" t="n">
-        <v>4.82</v>
       </c>
       <c r="H19" s="94" t="n">
         <v>4.82</v>
       </c>
       <c r="I19" s="94" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J19" s="94" t="n">
         <v>4.11</v>
-      </c>
-      <c r="J19" s="94" t="n">
-        <v>3.23</v>
       </c>
       <c r="K19" s="94" t="n">
         <v>3.23</v>
       </c>
       <c r="L19" s="94" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M19" s="94" t="n">
         <v>2.53</v>
       </c>
-      <c r="M19" s="94" t="n">
+      <c r="N19" s="94" t="n">
         <v>2.43</v>
       </c>
-      <c r="N19" s="94" t="n">
+      <c r="O19" s="94" t="n">
         <v>5.81</v>
       </c>
-      <c r="O19" s="94" t="n">
+      <c r="P19" s="94" t="n">
         <v>6.52</v>
-      </c>
-      <c r="P19" s="94" t="n">
-        <v>5.91</v>
       </c>
       <c r="Q19" s="94" t="n">
         <v>5.91</v>
       </c>
       <c r="R19" s="94" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="S19" s="94" t="n">
         <v>7.71</v>
       </c>
-      <c r="S19" s="94" t="n">
+      <c r="T19" s="94" t="n">
         <v>7.98</v>
       </c>
-      <c r="T19" s="94" t="n">
+      <c r="U19" s="94" t="n">
         <v>7.13</v>
       </c>
-      <c r="U19" s="94" t="n">
+      <c r="V19" s="94" t="n">
         <v>7.59</v>
-      </c>
-      <c r="V19" s="94" t="n">
-        <v>8.84</v>
       </c>
       <c r="W19" s="94" t="n">
         <v>8.84</v>
       </c>
       <c r="X19" s="94" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="Y19" s="94" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="Y19" s="94" t="n">
+      <c r="Z19" s="94" t="n">
         <v>10.75</v>
       </c>
-      <c r="Z19" s="94" t="n">
+      <c r="AA19" s="94" t="n">
         <v>10.58</v>
       </c>
-      <c r="AA19" s="94" t="n">
+      <c r="AB19" s="94" t="n">
         <v>11.81</v>
-      </c>
-      <c r="AB19" s="94" t="n">
-        <v>9.609999999999999</v>
       </c>
       <c r="AC19" s="94" t="n">
         <v>9.609999999999999</v>
       </c>
       <c r="AD19" s="94" t="n">
-        <v>8.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AE19" s="94" t="n">
-        <v>8.67</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -8544,94 +8542,94 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="C20" s="94" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D20" s="94" t="n">
         <v>4.85</v>
-      </c>
-      <c r="C20" s="94" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="D20" s="94" t="n">
-        <v>7.06</v>
       </c>
       <c r="E20" s="94" t="n">
         <v>7.06</v>
       </c>
       <c r="F20" s="94" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="G20" s="94" t="n">
         <v>8.34</v>
-      </c>
-      <c r="G20" s="94" t="n">
-        <v>8.49</v>
       </c>
       <c r="H20" s="94" t="n">
         <v>8.49</v>
       </c>
       <c r="I20" s="94" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="J20" s="94" t="n">
         <v>7.89</v>
-      </c>
-      <c r="J20" s="94" t="n">
-        <v>7.66</v>
       </c>
       <c r="K20" s="94" t="n">
         <v>7.66</v>
       </c>
       <c r="L20" s="94" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="M20" s="94" t="n">
         <v>7.16</v>
       </c>
-      <c r="M20" s="94" t="n">
+      <c r="N20" s="94" t="n">
         <v>7.54</v>
       </c>
-      <c r="N20" s="94" t="n">
+      <c r="O20" s="94" t="n">
         <v>10.35</v>
       </c>
-      <c r="O20" s="94" t="n">
+      <c r="P20" s="94" t="n">
         <v>10.88</v>
-      </c>
-      <c r="P20" s="94" t="n">
-        <v>10.64</v>
       </c>
       <c r="Q20" s="94" t="n">
         <v>10.64</v>
       </c>
       <c r="R20" s="94" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="S20" s="94" t="n">
         <v>11.08</v>
       </c>
-      <c r="S20" s="94" t="n">
+      <c r="T20" s="94" t="n">
         <v>11.34</v>
       </c>
-      <c r="T20" s="94" t="n">
+      <c r="U20" s="94" t="n">
         <v>10.26</v>
       </c>
-      <c r="U20" s="94" t="n">
+      <c r="V20" s="94" t="n">
         <v>10.31</v>
-      </c>
-      <c r="V20" s="94" t="n">
-        <v>11.27</v>
       </c>
       <c r="W20" s="94" t="n">
         <v>11.27</v>
       </c>
       <c r="X20" s="94" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="Y20" s="94" t="n">
         <v>11.85</v>
       </c>
-      <c r="Y20" s="94" t="n">
+      <c r="Z20" s="94" t="n">
         <v>12.01</v>
       </c>
-      <c r="Z20" s="94" t="n">
+      <c r="AA20" s="94" t="n">
         <v>11.6</v>
       </c>
-      <c r="AA20" s="94" t="n">
+      <c r="AB20" s="94" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB20" s="94" t="n">
-        <v>12.53</v>
       </c>
       <c r="AC20" s="94" t="n">
         <v>12.53</v>
       </c>
       <c r="AD20" s="94" t="n">
-        <v>12.19</v>
+        <v>12.53</v>
       </c>
       <c r="AE20" s="94" t="n">
-        <v>12.19</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -8641,94 +8639,94 @@
         </is>
       </c>
       <c r="B21" s="94" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="C21" s="94" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="D21" s="94" t="n">
         <v>11.56</v>
-      </c>
-      <c r="C21" s="94" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="D21" s="94" t="n">
-        <v>26.76</v>
       </c>
       <c r="E21" s="94" t="n">
         <v>26.76</v>
       </c>
       <c r="F21" s="94" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="G21" s="94" t="n">
         <v>85.53</v>
-      </c>
-      <c r="G21" s="94" t="n">
-        <v>89.12</v>
       </c>
       <c r="H21" s="94" t="n">
         <v>89.12</v>
       </c>
       <c r="I21" s="94" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="J21" s="94" t="n">
         <v>74.97</v>
-      </c>
-      <c r="J21" s="94" t="n">
-        <v>56.39</v>
       </c>
       <c r="K21" s="94" t="n">
         <v>56.39</v>
       </c>
       <c r="L21" s="94" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="M21" s="94" t="n">
         <v>3.51</v>
       </c>
-      <c r="M21" s="94" t="n">
+      <c r="N21" s="94" t="n">
         <v>3.69</v>
       </c>
-      <c r="N21" s="94" t="n">
+      <c r="O21" s="94" t="n">
         <v>33.91</v>
       </c>
-      <c r="O21" s="94" t="n">
+      <c r="P21" s="94" t="n">
         <v>73.43000000000001</v>
-      </c>
-      <c r="P21" s="94" t="n">
-        <v>38.09</v>
       </c>
       <c r="Q21" s="94" t="n">
         <v>38.09</v>
       </c>
       <c r="R21" s="94" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="S21" s="94" t="n">
         <v>38.26</v>
       </c>
-      <c r="S21" s="94" t="n">
+      <c r="T21" s="94" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="T21" s="94" t="n">
+      <c r="U21" s="94" t="n">
         <v>15.05</v>
       </c>
-      <c r="U21" s="94" t="n">
+      <c r="V21" s="94" t="n">
         <v>25.06</v>
-      </c>
-      <c r="V21" s="94" t="n">
-        <v>81.70999999999999</v>
       </c>
       <c r="W21" s="94" t="n">
         <v>81.70999999999999</v>
       </c>
       <c r="X21" s="94" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="Y21" s="94" t="n">
         <v>66.26000000000001</v>
       </c>
-      <c r="Y21" s="94" t="n">
+      <c r="Z21" s="94" t="n">
         <v>97.03</v>
       </c>
-      <c r="Z21" s="94" t="n">
+      <c r="AA21" s="94" t="n">
         <v>88.26000000000001</v>
       </c>
-      <c r="AA21" s="94" t="n">
+      <c r="AB21" s="94" t="n">
         <v>86.8</v>
-      </c>
-      <c r="AB21" s="94" t="n">
-        <v>80.16</v>
       </c>
       <c r="AC21" s="94" t="n">
         <v>80.16</v>
       </c>
       <c r="AD21" s="94" t="n">
-        <v>53.48</v>
+        <v>80.16</v>
       </c>
       <c r="AE21" s="94" t="n">
-        <v>53.48</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -8737,155 +8735,153 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C22" s="91" t="inlineStr">
+      <c r="E22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D22" s="93" t="inlineStr">
+      <c r="N22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E22" s="93" t="inlineStr">
+      <c r="X22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F22" s="93" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G22" s="93" t="inlineStr">
+      <c r="Z22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="93" t="inlineStr">
+      <c r="AA22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I22" s="93" t="inlineStr">
+      <c r="AB22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U22" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
+      <c r="AC22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC22" s="92" t="inlineStr">
+      <c r="AD22" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE22" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -8895,94 +8891,94 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C23" s="94" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D23" s="94" t="n">
         <v>1.34</v>
-      </c>
-      <c r="C23" s="94" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="D23" s="94" t="n">
-        <v>1.89</v>
       </c>
       <c r="E23" s="94" t="n">
         <v>1.89</v>
       </c>
       <c r="F23" s="94" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G23" s="94" t="n">
         <v>2.77</v>
-      </c>
-      <c r="G23" s="94" t="n">
-        <v>2.28</v>
       </c>
       <c r="H23" s="94" t="n">
         <v>2.28</v>
       </c>
       <c r="I23" s="94" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J23" s="94" t="n">
         <v>1.4</v>
-      </c>
-      <c r="J23" s="94" t="n">
-        <v>1.58</v>
       </c>
       <c r="K23" s="94" t="n">
         <v>1.58</v>
       </c>
       <c r="L23" s="94" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M23" s="94" t="n">
         <v>1.02</v>
       </c>
-      <c r="M23" s="94" t="n">
+      <c r="N23" s="94" t="n">
         <v>0.28</v>
       </c>
-      <c r="N23" s="94" t="n">
+      <c r="O23" s="94" t="n">
         <v>3.15</v>
       </c>
-      <c r="O23" s="94" t="n">
+      <c r="P23" s="94" t="n">
         <v>3.93</v>
-      </c>
-      <c r="P23" s="94" t="n">
-        <v>4.29</v>
       </c>
       <c r="Q23" s="94" t="n">
         <v>4.29</v>
       </c>
       <c r="R23" s="94" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="S23" s="94" t="n">
         <v>5.81</v>
       </c>
-      <c r="S23" s="94" t="n">
+      <c r="T23" s="94" t="n">
         <v>6.11</v>
       </c>
-      <c r="T23" s="94" t="n">
+      <c r="U23" s="94" t="n">
         <v>6.31</v>
       </c>
-      <c r="U23" s="94" t="n">
+      <c r="V23" s="94" t="n">
         <v>7.27</v>
-      </c>
-      <c r="V23" s="94" t="n">
-        <v>8.630000000000001</v>
       </c>
       <c r="W23" s="94" t="n">
         <v>8.630000000000001</v>
       </c>
       <c r="X23" s="94" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="Y23" s="94" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="Y23" s="94" t="n">
+      <c r="Z23" s="94" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z23" s="94" t="n">
+      <c r="AA23" s="94" t="n">
         <v>9.49</v>
       </c>
-      <c r="AA23" s="94" t="n">
+      <c r="AB23" s="94" t="n">
         <v>11</v>
-      </c>
-      <c r="AB23" s="94" t="n">
-        <v>10.19</v>
       </c>
       <c r="AC23" s="94" t="n">
         <v>10.19</v>
       </c>
       <c r="AD23" s="94" t="n">
-        <v>9.140000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="AE23" s="94" t="n">
-        <v>9.140000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -8992,94 +8988,94 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="C24" s="94" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="D24" s="94" t="n">
         <v>7.18</v>
-      </c>
-      <c r="C24" s="94" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="D24" s="94" t="n">
-        <v>9.42</v>
       </c>
       <c r="E24" s="94" t="n">
         <v>9.42</v>
       </c>
       <c r="F24" s="94" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="G24" s="94" t="n">
         <v>10.12</v>
-      </c>
-      <c r="G24" s="94" t="n">
-        <v>9.960000000000001</v>
       </c>
       <c r="H24" s="94" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="I24" s="94" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="J24" s="94" t="n">
         <v>9.16</v>
-      </c>
-      <c r="J24" s="94" t="n">
-        <v>8.92</v>
       </c>
       <c r="K24" s="94" t="n">
         <v>8.92</v>
       </c>
       <c r="L24" s="94" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="M24" s="94" t="n">
         <v>8.1</v>
       </c>
-      <c r="M24" s="94" t="n">
+      <c r="N24" s="94" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="N24" s="94" t="n">
+      <c r="O24" s="94" t="n">
         <v>10.94</v>
       </c>
-      <c r="O24" s="94" t="n">
+      <c r="P24" s="94" t="n">
         <v>11.73</v>
-      </c>
-      <c r="P24" s="94" t="n">
-        <v>12.06</v>
       </c>
       <c r="Q24" s="94" t="n">
         <v>12.06</v>
       </c>
       <c r="R24" s="94" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="S24" s="94" t="n">
         <v>11.43</v>
       </c>
-      <c r="S24" s="94" t="n">
+      <c r="T24" s="94" t="n">
         <v>12.77</v>
       </c>
-      <c r="T24" s="94" t="n">
+      <c r="U24" s="94" t="n">
         <v>13.07</v>
       </c>
-      <c r="U24" s="94" t="n">
+      <c r="V24" s="94" t="n">
         <v>14.34</v>
-      </c>
-      <c r="V24" s="94" t="n">
-        <v>15.12</v>
       </c>
       <c r="W24" s="94" t="n">
         <v>15.12</v>
       </c>
       <c r="X24" s="94" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="Y24" s="94" t="n">
         <v>16.01</v>
       </c>
-      <c r="Y24" s="94" t="n">
+      <c r="Z24" s="94" t="n">
         <v>16.47</v>
       </c>
-      <c r="Z24" s="94" t="n">
+      <c r="AA24" s="94" t="n">
         <v>15.48</v>
       </c>
-      <c r="AA24" s="94" t="n">
+      <c r="AB24" s="94" t="n">
         <v>15.57</v>
-      </c>
-      <c r="AB24" s="94" t="n">
-        <v>15.55</v>
       </c>
       <c r="AC24" s="94" t="n">
         <v>15.55</v>
       </c>
       <c r="AD24" s="94" t="n">
-        <v>15.27</v>
+        <v>15.55</v>
       </c>
       <c r="AE24" s="94" t="n">
-        <v>15.27</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -9089,94 +9085,94 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="C25" s="94" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="D25" s="94" t="n">
         <v>22.32</v>
-      </c>
-      <c r="C25" s="94" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="D25" s="94" t="n">
-        <v>40.35</v>
       </c>
       <c r="E25" s="94" t="n">
         <v>40.35</v>
       </c>
       <c r="F25" s="94" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="G25" s="94" t="n">
         <v>70.73999999999999</v>
-      </c>
-      <c r="G25" s="94" t="n">
-        <v>69.41</v>
       </c>
       <c r="H25" s="94" t="n">
         <v>69.41</v>
       </c>
       <c r="I25" s="94" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="J25" s="94" t="n">
         <v>48.25</v>
-      </c>
-      <c r="J25" s="94" t="n">
-        <v>43.82</v>
       </c>
       <c r="K25" s="94" t="n">
         <v>43.82</v>
       </c>
       <c r="L25" s="94" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="M25" s="94" t="n">
         <v>2.07</v>
       </c>
-      <c r="M25" s="94" t="n">
+      <c r="N25" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="N25" s="94" t="n">
+      <c r="O25" s="94" t="n">
         <v>2.24</v>
       </c>
-      <c r="O25" s="94" t="n">
+      <c r="P25" s="94" t="n">
         <v>4.42</v>
-      </c>
-      <c r="P25" s="94" t="n">
-        <v>6.04</v>
       </c>
       <c r="Q25" s="94" t="n">
         <v>6.04</v>
       </c>
       <c r="R25" s="94" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="S25" s="94" t="n">
         <v>7.45</v>
       </c>
-      <c r="S25" s="94" t="n">
+      <c r="T25" s="94" t="n">
         <v>12.97</v>
       </c>
-      <c r="T25" s="94" t="n">
+      <c r="U25" s="94" t="n">
         <v>16.4</v>
       </c>
-      <c r="U25" s="94" t="n">
+      <c r="V25" s="94" t="n">
         <v>22.57</v>
-      </c>
-      <c r="V25" s="94" t="n">
-        <v>37.12</v>
       </c>
       <c r="W25" s="94" t="n">
         <v>37.12</v>
       </c>
       <c r="X25" s="94" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="Y25" s="94" t="n">
         <v>47.59</v>
       </c>
-      <c r="Y25" s="94" t="n">
+      <c r="Z25" s="94" t="n">
         <v>76.63</v>
       </c>
-      <c r="Z25" s="94" t="n">
+      <c r="AA25" s="94" t="n">
         <v>52.74</v>
       </c>
-      <c r="AA25" s="94" t="n">
+      <c r="AB25" s="94" t="n">
         <v>63.46</v>
-      </c>
-      <c r="AB25" s="94" t="n">
-        <v>82.20999999999999</v>
       </c>
       <c r="AC25" s="94" t="n">
         <v>82.20999999999999</v>
       </c>
       <c r="AD25" s="94" t="n">
-        <v>74.98999999999999</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="AE25" s="94" t="n">
-        <v>74.98999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -9205,135 +9201,133 @@
           <t>green</t>
         </is>
       </c>
-      <c r="F26" s="92" t="inlineStr">
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="92" t="inlineStr">
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="92" t="inlineStr">
+      <c r="I26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="J26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J26" s="91" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K26" s="91" t="inlineStr">
+      <c r="L26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L26" s="91" t="inlineStr">
+      <c r="M26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M26" s="91" t="inlineStr">
+      <c r="N26" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N26" s="93" t="inlineStr">
+      <c r="O26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O26" s="92" t="inlineStr">
+      <c r="P26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P26" s="93" t="inlineStr">
+      <c r="Q26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q26" s="93" t="inlineStr">
+      <c r="R26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="S26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S26" s="92" t="inlineStr">
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="U26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U26" s="93" t="inlineStr">
+      <c r="V26" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V26" s="92" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W26" s="92" t="inlineStr">
+      <c r="X26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X26" s="92" t="inlineStr">
+      <c r="Y26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y26" s="92" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z26" s="92" t="inlineStr">
+      <c r="AA26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA26" s="92" t="inlineStr">
+      <c r="AB26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB26" s="92" t="inlineStr">
+      <c r="AC26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC26" s="92" t="inlineStr">
+      <c r="AD26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
+      <c r="AE26" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -9346,91 +9340,91 @@
         <v>6.47</v>
       </c>
       <c r="C27" s="94" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="D27" s="94" t="n">
         <v>8.75</v>
-      </c>
-      <c r="D27" s="94" t="n">
-        <v>10.02</v>
       </c>
       <c r="E27" s="94" t="n">
         <v>10.02</v>
       </c>
       <c r="F27" s="94" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="G27" s="94" t="n">
         <v>11.78</v>
-      </c>
-      <c r="G27" s="94" t="n">
-        <v>10.13</v>
       </c>
       <c r="H27" s="94" t="n">
         <v>10.13</v>
       </c>
       <c r="I27" s="94" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="J27" s="94" t="n">
         <v>9.08</v>
-      </c>
-      <c r="J27" s="94" t="n">
-        <v>7.6</v>
       </c>
       <c r="K27" s="94" t="n">
         <v>7.6</v>
       </c>
       <c r="L27" s="94" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M27" s="94" t="n">
         <v>7.14</v>
       </c>
-      <c r="M27" s="94" t="n">
+      <c r="N27" s="94" t="n">
         <v>7.29</v>
       </c>
-      <c r="N27" s="94" t="n">
+      <c r="O27" s="94" t="n">
         <v>11.88</v>
       </c>
-      <c r="O27" s="94" t="n">
+      <c r="P27" s="94" t="n">
         <v>12.4</v>
-      </c>
-      <c r="P27" s="94" t="n">
-        <v>10.62</v>
       </c>
       <c r="Q27" s="94" t="n">
         <v>10.62</v>
       </c>
       <c r="R27" s="94" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="S27" s="94" t="n">
         <v>13.26</v>
       </c>
-      <c r="S27" s="94" t="n">
+      <c r="T27" s="94" t="n">
         <v>13.65</v>
       </c>
-      <c r="T27" s="94" t="n">
+      <c r="U27" s="94" t="n">
         <v>11.91</v>
       </c>
-      <c r="U27" s="94" t="n">
+      <c r="V27" s="94" t="n">
         <v>11.61</v>
-      </c>
-      <c r="V27" s="94" t="n">
-        <v>13.03</v>
       </c>
       <c r="W27" s="94" t="n">
         <v>13.03</v>
       </c>
       <c r="X27" s="94" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="Y27" s="94" t="n">
         <v>13.25</v>
       </c>
-      <c r="Y27" s="94" t="n">
+      <c r="Z27" s="94" t="n">
         <v>15.91</v>
       </c>
-      <c r="Z27" s="94" t="n">
+      <c r="AA27" s="94" t="n">
         <v>15.38</v>
       </c>
-      <c r="AA27" s="94" t="n">
+      <c r="AB27" s="94" t="n">
         <v>16.26</v>
-      </c>
-      <c r="AB27" s="94" t="n">
-        <v>12.21</v>
       </c>
       <c r="AC27" s="94" t="n">
         <v>12.21</v>
       </c>
       <c r="AD27" s="94" t="n">
-        <v>11.57</v>
+        <v>12.21</v>
       </c>
       <c r="AE27" s="94" t="n">
-        <v>11.57</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -9443,91 +9437,91 @@
         <v>5.62</v>
       </c>
       <c r="C28" s="94" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D28" s="94" t="n">
         <v>4.5</v>
-      </c>
-      <c r="D28" s="94" t="n">
-        <v>7.01</v>
       </c>
       <c r="E28" s="94" t="n">
         <v>7.01</v>
       </c>
       <c r="F28" s="94" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G28" s="94" t="n">
         <v>8.779999999999999</v>
-      </c>
-      <c r="G28" s="94" t="n">
-        <v>9.15</v>
       </c>
       <c r="H28" s="94" t="n">
         <v>9.15</v>
       </c>
       <c r="I28" s="94" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J28" s="94" t="n">
         <v>8.67</v>
-      </c>
-      <c r="J28" s="94" t="n">
-        <v>8.56</v>
       </c>
       <c r="K28" s="94" t="n">
         <v>8.56</v>
       </c>
       <c r="L28" s="94" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="M28" s="94" t="n">
         <v>8.35</v>
       </c>
-      <c r="M28" s="94" t="n">
+      <c r="N28" s="94" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="N28" s="94" t="n">
+      <c r="O28" s="94" t="n">
         <v>12.6</v>
       </c>
-      <c r="O28" s="94" t="n">
+      <c r="P28" s="94" t="n">
         <v>13.3</v>
-      </c>
-      <c r="P28" s="94" t="n">
-        <v>12.47</v>
       </c>
       <c r="Q28" s="94" t="n">
         <v>12.47</v>
       </c>
       <c r="R28" s="94" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="S28" s="94" t="n">
         <v>13.75</v>
       </c>
-      <c r="S28" s="94" t="n">
+      <c r="T28" s="94" t="n">
         <v>13.26</v>
       </c>
-      <c r="T28" s="94" t="n">
+      <c r="U28" s="94" t="n">
         <v>11.09</v>
       </c>
-      <c r="U28" s="94" t="n">
+      <c r="V28" s="94" t="n">
         <v>10.49</v>
-      </c>
-      <c r="V28" s="94" t="n">
-        <v>11.22</v>
       </c>
       <c r="W28" s="94" t="n">
         <v>11.22</v>
       </c>
       <c r="X28" s="94" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="Y28" s="94" t="n">
         <v>11.37</v>
       </c>
-      <c r="Y28" s="94" t="n">
+      <c r="Z28" s="94" t="n">
         <v>11.7</v>
       </c>
-      <c r="Z28" s="94" t="n">
+      <c r="AA28" s="94" t="n">
         <v>10.63</v>
       </c>
-      <c r="AA28" s="94" t="n">
+      <c r="AB28" s="94" t="n">
         <v>11.88</v>
-      </c>
-      <c r="AB28" s="94" t="n">
-        <v>11.78</v>
       </c>
       <c r="AC28" s="94" t="n">
         <v>11.78</v>
       </c>
       <c r="AD28" s="94" t="n">
-        <v>11.25</v>
+        <v>11.78</v>
       </c>
       <c r="AE28" s="94" t="n">
-        <v>11.25</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -9540,91 +9534,91 @@
         <v>6.54</v>
       </c>
       <c r="C29" s="94" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D29" s="94" t="n">
         <v>11.7</v>
-      </c>
-      <c r="D29" s="94" t="n">
-        <v>24.8</v>
       </c>
       <c r="E29" s="94" t="n">
         <v>24.8</v>
       </c>
       <c r="F29" s="94" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G29" s="94" t="n">
         <v>85.38</v>
-      </c>
-      <c r="G29" s="94" t="n">
-        <v>89.31</v>
       </c>
       <c r="H29" s="94" t="n">
         <v>89.31</v>
       </c>
       <c r="I29" s="94" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="J29" s="94" t="n">
         <v>75.14</v>
-      </c>
-      <c r="J29" s="94" t="n">
-        <v>52.31</v>
       </c>
       <c r="K29" s="94" t="n">
         <v>52.31</v>
       </c>
       <c r="L29" s="94" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="M29" s="94" t="n">
         <v>8.75</v>
       </c>
-      <c r="M29" s="94" t="n">
+      <c r="N29" s="94" t="n">
         <v>9.17</v>
       </c>
-      <c r="N29" s="94" t="n">
+      <c r="O29" s="94" t="n">
         <v>64.33</v>
       </c>
-      <c r="O29" s="94" t="n">
+      <c r="P29" s="94" t="n">
         <v>88.39</v>
-      </c>
-      <c r="P29" s="94" t="n">
-        <v>59.57</v>
       </c>
       <c r="Q29" s="94" t="n">
         <v>59.57</v>
       </c>
       <c r="R29" s="94" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="S29" s="94" t="n">
         <v>54.06</v>
       </c>
-      <c r="S29" s="94" t="n">
+      <c r="T29" s="94" t="n">
         <v>86.75</v>
       </c>
-      <c r="T29" s="94" t="n">
+      <c r="U29" s="94" t="n">
         <v>35.1</v>
       </c>
-      <c r="U29" s="94" t="n">
+      <c r="V29" s="94" t="n">
         <v>48.55</v>
-      </c>
-      <c r="V29" s="94" t="n">
-        <v>92.86</v>
       </c>
       <c r="W29" s="94" t="n">
         <v>92.86</v>
       </c>
       <c r="X29" s="94" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="Y29" s="94" t="n">
         <v>82.54000000000001</v>
       </c>
-      <c r="Y29" s="94" t="n">
+      <c r="Z29" s="94" t="n">
         <v>98.04000000000001</v>
       </c>
-      <c r="Z29" s="94" t="n">
+      <c r="AA29" s="94" t="n">
         <v>93.78</v>
       </c>
-      <c r="AA29" s="94" t="n">
+      <c r="AB29" s="94" t="n">
         <v>90.73</v>
-      </c>
-      <c r="AB29" s="94" t="n">
-        <v>77.28</v>
       </c>
       <c r="AC29" s="94" t="n">
         <v>77.28</v>
       </c>
       <c r="AD29" s="94" t="n">
-        <v>40.96</v>
+        <v>77.28</v>
       </c>
       <c r="AE29" s="94" t="n">
-        <v>40.96</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -9663,124 +9657,124 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H30" s="91" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I30" s="92" t="inlineStr">
+      <c r="J30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J30" s="91" t="inlineStr">
+      <c r="K30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K30" s="91" t="inlineStr">
+      <c r="L30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L30" s="91" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="91" t="inlineStr">
+      <c r="N30" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N30" s="93" t="inlineStr">
+      <c r="O30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O30" s="93" t="inlineStr">
+      <c r="P30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P30" s="93" t="inlineStr">
+      <c r="Q30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="R30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R30" s="92" t="inlineStr">
+      <c r="S30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S30" s="93" t="inlineStr">
+      <c r="T30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T30" s="92" t="inlineStr">
+      <c r="U30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U30" s="93" t="inlineStr">
+      <c r="V30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V30" s="93" t="inlineStr">
+      <c r="W30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W30" s="93" t="inlineStr">
+      <c r="X30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X30" s="92" t="inlineStr">
+      <c r="Y30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y30" s="92" t="inlineStr">
+      <c r="Z30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z30" s="92" t="inlineStr">
+      <c r="AA30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA30" s="92" t="inlineStr">
+      <c r="AB30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB30" s="93" t="inlineStr">
+      <c r="AC30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC30" s="93" t="inlineStr">
+      <c r="AD30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD30" s="93" t="inlineStr">
+      <c r="AE30" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE30" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -9797,88 +9791,88 @@
         <v>3.26</v>
       </c>
       <c r="D31" s="94" t="n">
-        <v>4.49</v>
+        <v>3.26</v>
       </c>
       <c r="E31" s="94" t="n">
         <v>4.49</v>
       </c>
       <c r="F31" s="94" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G31" s="94" t="n">
         <v>4.65</v>
       </c>
-      <c r="G31" s="94" t="n">
+      <c r="H31" s="94" t="n">
         <v>1.24</v>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="I31" s="94" t="n">
         <v>2.95</v>
       </c>
-      <c r="I31" s="94" t="n">
+      <c r="J31" s="94" t="n">
         <v>-1.68</v>
-      </c>
-      <c r="J31" s="94" t="n">
-        <v>-0.57</v>
       </c>
       <c r="K31" s="94" t="n">
         <v>-0.57</v>
       </c>
       <c r="L31" s="94" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M31" s="94" t="n">
         <v>2.49</v>
       </c>
-      <c r="M31" s="94" t="n">
+      <c r="N31" s="94" t="n">
         <v>3.01</v>
       </c>
-      <c r="N31" s="94" t="n">
+      <c r="O31" s="94" t="n">
         <v>4.35</v>
       </c>
-      <c r="O31" s="94" t="n">
+      <c r="P31" s="94" t="n">
         <v>6.2</v>
-      </c>
-      <c r="P31" s="94" t="n">
-        <v>8.49</v>
       </c>
       <c r="Q31" s="94" t="n">
         <v>8.49</v>
       </c>
       <c r="R31" s="94" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="S31" s="94" t="n">
         <v>10.07</v>
       </c>
-      <c r="S31" s="94" t="n">
+      <c r="T31" s="94" t="n">
         <v>7.7</v>
       </c>
-      <c r="T31" s="94" t="n">
+      <c r="U31" s="94" t="n">
         <v>7.62</v>
       </c>
-      <c r="U31" s="94" t="n">
+      <c r="V31" s="94" t="n">
         <v>6.32</v>
-      </c>
-      <c r="V31" s="94" t="n">
-        <v>9.75</v>
       </c>
       <c r="W31" s="94" t="n">
         <v>9.75</v>
       </c>
       <c r="X31" s="94" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="Y31" s="94" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="Y31" s="94" t="n">
+      <c r="Z31" s="94" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="Z31" s="94" t="n">
+      <c r="AA31" s="94" t="n">
         <v>7.85</v>
       </c>
-      <c r="AA31" s="94" t="n">
+      <c r="AB31" s="94" t="n">
         <v>5.06</v>
-      </c>
-      <c r="AB31" s="94" t="n">
-        <v>3.13</v>
       </c>
       <c r="AC31" s="94" t="n">
         <v>3.13</v>
       </c>
       <c r="AD31" s="94" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE31" s="94" t="n">
         <v>-0.87</v>
-      </c>
-      <c r="AE31" s="94" t="n">
-        <v>-1.46</v>
       </c>
     </row>
     <row r="32">
@@ -9894,88 +9888,88 @@
         <v>-4.63</v>
       </c>
       <c r="D32" s="94" t="n">
-        <v>-3.12</v>
+        <v>-4.63</v>
       </c>
       <c r="E32" s="94" t="n">
         <v>-3.12</v>
       </c>
       <c r="F32" s="94" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="G32" s="94" t="n">
         <v>-2.97</v>
       </c>
-      <c r="G32" s="94" t="n">
+      <c r="H32" s="94" t="n">
         <v>-4.36</v>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="I32" s="94" t="n">
         <v>-4.59</v>
       </c>
-      <c r="I32" s="94" t="n">
+      <c r="J32" s="94" t="n">
         <v>-3.5</v>
-      </c>
-      <c r="J32" s="94" t="n">
-        <v>-3.43</v>
       </c>
       <c r="K32" s="94" t="n">
         <v>-3.43</v>
       </c>
       <c r="L32" s="94" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="M32" s="94" t="n">
         <v>-2.06</v>
       </c>
-      <c r="M32" s="94" t="n">
+      <c r="N32" s="94" t="n">
         <v>-1.27</v>
       </c>
-      <c r="N32" s="94" t="n">
+      <c r="O32" s="94" t="n">
         <v>0.06</v>
       </c>
-      <c r="O32" s="94" t="n">
+      <c r="P32" s="94" t="n">
         <v>-0.53</v>
-      </c>
-      <c r="P32" s="94" t="n">
-        <v>0.76</v>
       </c>
       <c r="Q32" s="94" t="n">
         <v>0.76</v>
       </c>
       <c r="R32" s="94" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S32" s="94" t="n">
         <v>2.69</v>
       </c>
-      <c r="S32" s="94" t="n">
+      <c r="T32" s="94" t="n">
         <v>2.01</v>
       </c>
-      <c r="T32" s="94" t="n">
+      <c r="U32" s="94" t="n">
         <v>1.9</v>
       </c>
-      <c r="U32" s="94" t="n">
+      <c r="V32" s="94" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V32" s="94" t="n">
-        <v>1.58</v>
       </c>
       <c r="W32" s="94" t="n">
         <v>1.58</v>
       </c>
       <c r="X32" s="94" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y32" s="94" t="n">
         <v>3.39</v>
       </c>
-      <c r="Y32" s="94" t="n">
+      <c r="Z32" s="94" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z32" s="94" t="n">
+      <c r="AA32" s="94" t="n">
         <v>1.36</v>
       </c>
-      <c r="AA32" s="94" t="n">
+      <c r="AB32" s="94" t="n">
         <v>-0.9399999999999999</v>
-      </c>
-      <c r="AB32" s="94" t="n">
-        <v>-2.37</v>
       </c>
       <c r="AC32" s="94" t="n">
         <v>-2.37</v>
       </c>
       <c r="AD32" s="94" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="AE32" s="94" t="n">
         <v>-1.77</v>
-      </c>
-      <c r="AE32" s="94" t="n">
-        <v>-1.42</v>
       </c>
     </row>
     <row r="33">
@@ -9991,88 +9985,88 @@
         <v>61.59</v>
       </c>
       <c r="D33" s="94" t="n">
-        <v>71.7</v>
+        <v>61.59</v>
       </c>
       <c r="E33" s="94" t="n">
         <v>71.7</v>
       </c>
       <c r="F33" s="94" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="G33" s="94" t="n">
         <v>61.28</v>
       </c>
-      <c r="G33" s="94" t="n">
+      <c r="H33" s="94" t="n">
         <v>51.56</v>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="I33" s="94" t="n">
         <v>49.14</v>
       </c>
-      <c r="I33" s="94" t="n">
+      <c r="J33" s="94" t="n">
         <v>52.23</v>
-      </c>
-      <c r="J33" s="94" t="n">
-        <v>39.79</v>
       </c>
       <c r="K33" s="94" t="n">
         <v>39.79</v>
       </c>
       <c r="L33" s="94" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="M33" s="94" t="n">
         <v>42.16</v>
       </c>
-      <c r="M33" s="94" t="n">
+      <c r="N33" s="94" t="n">
         <v>48.31</v>
       </c>
-      <c r="N33" s="94" t="n">
+      <c r="O33" s="94" t="n">
         <v>55.97</v>
       </c>
-      <c r="O33" s="94" t="n">
+      <c r="P33" s="94" t="n">
         <v>58.68</v>
-      </c>
-      <c r="P33" s="94" t="n">
-        <v>59.03</v>
       </c>
       <c r="Q33" s="94" t="n">
         <v>59.03</v>
       </c>
       <c r="R33" s="94" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="S33" s="94" t="n">
         <v>70.04000000000001</v>
       </c>
-      <c r="S33" s="94" t="n">
+      <c r="T33" s="94" t="n">
         <v>62.14</v>
       </c>
-      <c r="T33" s="94" t="n">
+      <c r="U33" s="94" t="n">
         <v>62.05</v>
       </c>
-      <c r="U33" s="94" t="n">
+      <c r="V33" s="94" t="n">
         <v>58.27</v>
-      </c>
-      <c r="V33" s="94" t="n">
-        <v>56.99</v>
       </c>
       <c r="W33" s="94" t="n">
         <v>56.99</v>
       </c>
       <c r="X33" s="94" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="Y33" s="94" t="n">
         <v>64.72</v>
       </c>
-      <c r="Y33" s="94" t="n">
+      <c r="Z33" s="94" t="n">
         <v>62.97</v>
       </c>
-      <c r="Z33" s="94" t="n">
+      <c r="AA33" s="94" t="n">
         <v>62.59</v>
       </c>
-      <c r="AA33" s="94" t="n">
+      <c r="AB33" s="94" t="n">
         <v>50.52</v>
-      </c>
-      <c r="AB33" s="94" t="n">
-        <v>43.84</v>
       </c>
       <c r="AC33" s="94" t="n">
         <v>43.84</v>
       </c>
       <c r="AD33" s="94" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AE33" s="94" t="n">
         <v>46.41</v>
-      </c>
-      <c r="AE33" s="94" t="n">
-        <v>41.8</v>
       </c>
     </row>
     <row r="34">
@@ -10091,119 +10085,119 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D34" s="92" t="inlineStr">
+      <c r="D34" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="F34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F34" s="92" t="inlineStr">
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G34" s="92" t="inlineStr">
+      <c r="H34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H34" s="93" t="inlineStr">
+      <c r="I34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I34" s="93" t="inlineStr">
+      <c r="J34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J34" s="91" t="inlineStr">
+      <c r="K34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K34" s="91" t="inlineStr">
+      <c r="L34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L34" s="91" t="inlineStr">
+      <c r="M34" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="N34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="O34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="P34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P34" s="93" t="inlineStr">
+      <c r="Q34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q34" s="93" t="inlineStr">
+      <c r="R34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="S34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="T34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="U34" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U34" s="92" t="inlineStr">
+      <c r="V34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V34" s="92" t="inlineStr">
+      <c r="W34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W34" s="92" t="inlineStr">
+      <c r="X34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X34" s="92" t="inlineStr">
+      <c r="Y34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y34" s="91" t="inlineStr">
+      <c r="Z34" s="91" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z34" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AA34" s="92" t="inlineStr">
@@ -10242,91 +10236,91 @@
         <v>-0.41</v>
       </c>
       <c r="C35" s="94" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="D35" s="94" t="n">
         <v>0.16</v>
-      </c>
-      <c r="D35" s="94" t="n">
-        <v>0.36</v>
       </c>
       <c r="E35" s="94" t="n">
         <v>0.36</v>
       </c>
       <c r="F35" s="94" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G35" s="94" t="n">
         <v>-0.41</v>
       </c>
-      <c r="G35" s="94" t="n">
+      <c r="H35" s="94" t="n">
         <v>-1.07</v>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="I35" s="94" t="n">
         <v>-2.46</v>
       </c>
-      <c r="I35" s="94" t="n">
+      <c r="J35" s="94" t="n">
         <v>-1.96</v>
-      </c>
-      <c r="J35" s="94" t="n">
-        <v>-2.59</v>
       </c>
       <c r="K35" s="94" t="n">
         <v>-2.59</v>
       </c>
       <c r="L35" s="94" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="M35" s="94" t="n">
         <v>-2.85</v>
       </c>
-      <c r="M35" s="94" t="n">
+      <c r="N35" s="94" t="n">
         <v>-1.67</v>
       </c>
-      <c r="N35" s="94" t="n">
+      <c r="O35" s="94" t="n">
         <v>-1.2</v>
       </c>
-      <c r="O35" s="94" t="n">
+      <c r="P35" s="94" t="n">
         <v>-0.37</v>
-      </c>
-      <c r="P35" s="94" t="n">
-        <v>-0.74</v>
       </c>
       <c r="Q35" s="94" t="n">
         <v>-0.74</v>
       </c>
       <c r="R35" s="94" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="S35" s="94" t="n">
         <v>-0.31</v>
       </c>
-      <c r="S35" s="94" t="n">
+      <c r="T35" s="94" t="n">
         <v>0.31</v>
       </c>
-      <c r="T35" s="94" t="n">
+      <c r="U35" s="94" t="n">
         <v>1.04</v>
       </c>
-      <c r="U35" s="94" t="n">
+      <c r="V35" s="94" t="n">
         <v>2.79</v>
-      </c>
-      <c r="V35" s="94" t="n">
-        <v>1.47</v>
       </c>
       <c r="W35" s="94" t="n">
         <v>1.47</v>
       </c>
       <c r="X35" s="94" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y35" s="94" t="n">
         <v>0.89</v>
       </c>
-      <c r="Y35" s="94" t="n">
+      <c r="Z35" s="94" t="n">
         <v>-1.03</v>
       </c>
-      <c r="Z35" s="94" t="n">
+      <c r="AA35" s="94" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AA35" s="94" t="n">
+      <c r="AB35" s="94" t="n">
         <v>-1.3</v>
-      </c>
-      <c r="AB35" s="94" t="n">
-        <v>-1.84</v>
       </c>
       <c r="AC35" s="94" t="n">
         <v>-1.84</v>
       </c>
       <c r="AD35" s="94" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="AE35" s="94" t="n">
         <v>-2.06</v>
-      </c>
-      <c r="AE35" s="94" t="n">
-        <v>-2.65</v>
       </c>
     </row>
     <row r="36">
@@ -10339,91 +10333,91 @@
         <v>-1.09</v>
       </c>
       <c r="C36" s="94" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="D36" s="94" t="n">
         <v>-0.92</v>
-      </c>
-      <c r="D36" s="94" t="n">
-        <v>-0.84</v>
       </c>
       <c r="E36" s="94" t="n">
         <v>-0.84</v>
       </c>
       <c r="F36" s="94" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="G36" s="94" t="n">
         <v>-1.61</v>
       </c>
-      <c r="G36" s="94" t="n">
+      <c r="H36" s="94" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="I36" s="94" t="n">
         <v>-1.77</v>
       </c>
-      <c r="I36" s="94" t="n">
+      <c r="J36" s="94" t="n">
         <v>-1.34</v>
-      </c>
-      <c r="J36" s="94" t="n">
-        <v>-1.52</v>
       </c>
       <c r="K36" s="94" t="n">
         <v>-1.52</v>
       </c>
       <c r="L36" s="94" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="M36" s="94" t="n">
         <v>-1.19</v>
       </c>
-      <c r="M36" s="94" t="n">
+      <c r="N36" s="94" t="n">
         <v>0.91</v>
       </c>
-      <c r="N36" s="94" t="n">
+      <c r="O36" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="O36" s="94" t="n">
+      <c r="P36" s="94" t="n">
         <v>1.48</v>
-      </c>
-      <c r="P36" s="94" t="n">
-        <v>0.28</v>
       </c>
       <c r="Q36" s="94" t="n">
         <v>0.28</v>
       </c>
       <c r="R36" s="94" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="S36" s="94" t="n">
+      <c r="T36" s="94" t="n">
         <v>0.98</v>
       </c>
-      <c r="T36" s="94" t="n">
+      <c r="U36" s="94" t="n">
         <v>1.43</v>
       </c>
-      <c r="U36" s="94" t="n">
+      <c r="V36" s="94" t="n">
         <v>-0.64</v>
-      </c>
-      <c r="V36" s="94" t="n">
-        <v>-0.95</v>
       </c>
       <c r="W36" s="94" t="n">
         <v>-0.95</v>
       </c>
       <c r="X36" s="94" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="Y36" s="94" t="n">
         <v>-0.96</v>
       </c>
-      <c r="Y36" s="94" t="n">
+      <c r="Z36" s="94" t="n">
         <v>-3.06</v>
       </c>
-      <c r="Z36" s="94" t="n">
+      <c r="AA36" s="94" t="n">
         <v>-1.96</v>
       </c>
-      <c r="AA36" s="94" t="n">
+      <c r="AB36" s="94" t="n">
         <v>-2.24</v>
-      </c>
-      <c r="AB36" s="94" t="n">
-        <v>-3.92</v>
       </c>
       <c r="AC36" s="94" t="n">
         <v>-3.92</v>
       </c>
       <c r="AD36" s="94" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="AE36" s="94" t="n">
         <v>-4.47</v>
-      </c>
-      <c r="AE36" s="94" t="n">
-        <v>-3.3</v>
       </c>
     </row>
     <row r="37">
@@ -10436,91 +10430,91 @@
         <v>34.51</v>
       </c>
       <c r="C37" s="94" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="D37" s="94" t="n">
         <v>57.76</v>
-      </c>
-      <c r="D37" s="94" t="n">
-        <v>78.84999999999999</v>
       </c>
       <c r="E37" s="94" t="n">
         <v>78.84999999999999</v>
       </c>
       <c r="F37" s="94" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="G37" s="94" t="n">
         <v>74.3</v>
       </c>
-      <c r="G37" s="94" t="n">
+      <c r="H37" s="94" t="n">
         <v>80.23</v>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="I37" s="94" t="n">
         <v>47.65</v>
       </c>
-      <c r="I37" s="94" t="n">
+      <c r="J37" s="94" t="n">
         <v>59.03</v>
-      </c>
-      <c r="J37" s="94" t="n">
-        <v>37.08</v>
       </c>
       <c r="K37" s="94" t="n">
         <v>37.08</v>
       </c>
       <c r="L37" s="94" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="M37" s="94" t="n">
         <v>22.12</v>
       </c>
-      <c r="M37" s="94" t="n">
+      <c r="N37" s="94" t="n">
         <v>60.56</v>
       </c>
-      <c r="N37" s="94" t="n">
+      <c r="O37" s="94" t="n">
         <v>29.86</v>
       </c>
-      <c r="O37" s="94" t="n">
+      <c r="P37" s="94" t="n">
         <v>39.86</v>
-      </c>
-      <c r="P37" s="94" t="n">
-        <v>30.75</v>
       </c>
       <c r="Q37" s="94" t="n">
         <v>30.75</v>
       </c>
       <c r="R37" s="94" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="S37" s="94" t="n">
         <v>50.9</v>
       </c>
-      <c r="S37" s="94" t="n">
+      <c r="T37" s="94" t="n">
         <v>59.05</v>
       </c>
-      <c r="T37" s="94" t="n">
+      <c r="U37" s="94" t="n">
         <v>76.38</v>
       </c>
-      <c r="U37" s="94" t="n">
+      <c r="V37" s="94" t="n">
         <v>85.62</v>
-      </c>
-      <c r="V37" s="94" t="n">
-        <v>82.7</v>
       </c>
       <c r="W37" s="94" t="n">
         <v>82.7</v>
       </c>
       <c r="X37" s="94" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Y37" s="94" t="n">
         <v>80.88</v>
       </c>
-      <c r="Y37" s="94" t="n">
+      <c r="Z37" s="94" t="n">
         <v>29.16</v>
       </c>
-      <c r="Z37" s="94" t="n">
+      <c r="AA37" s="94" t="n">
         <v>78.03</v>
       </c>
-      <c r="AA37" s="94" t="n">
+      <c r="AB37" s="94" t="n">
         <v>93.29000000000001</v>
-      </c>
-      <c r="AB37" s="94" t="n">
-        <v>92.78</v>
       </c>
       <c r="AC37" s="94" t="n">
         <v>92.78</v>
       </c>
       <c r="AD37" s="94" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="AE37" s="94" t="n">
         <v>83.34999999999999</v>
-      </c>
-      <c r="AE37" s="94" t="n">
-        <v>83.11</v>
       </c>
     </row>
     <row r="38">
@@ -10554,129 +10548,129 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="91" t="inlineStr">
+      <c r="G38" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H38" s="91" t="inlineStr">
+      <c r="I38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="91" t="inlineStr">
+      <c r="J38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J38" s="91" t="inlineStr">
+      <c r="K38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K38" s="91" t="inlineStr">
+      <c r="L38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L38" s="91" t="inlineStr">
+      <c r="M38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M38" s="91" t="inlineStr">
+      <c r="N38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N38" s="91" t="inlineStr">
+      <c r="O38" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O38" s="93" t="inlineStr">
+      <c r="P38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P38" s="92" t="inlineStr">
+      <c r="Q38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q38" s="92" t="inlineStr">
+      <c r="R38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R38" s="93" t="inlineStr">
+      <c r="S38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S38" s="93" t="inlineStr">
+      <c r="T38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T38" s="93" t="inlineStr">
+      <c r="U38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U38" s="93" t="inlineStr">
+      <c r="V38" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V38" s="92" t="inlineStr">
+      <c r="W38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W38" s="92" t="inlineStr">
+      <c r="X38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X38" s="92" t="inlineStr">
+      <c r="Y38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y38" s="92" t="inlineStr">
+      <c r="Z38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z38" s="92" t="inlineStr">
+      <c r="AA38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA38" s="92" t="inlineStr">
+      <c r="AB38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB38" s="92" t="inlineStr">
+      <c r="AC38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC38" s="92" t="inlineStr">
+      <c r="AD38" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD38" s="91" t="inlineStr">
+      <c r="AE38" s="91" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10687,94 +10681,94 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="C39" s="94" t="n">
         <v>-5.28</v>
       </c>
-      <c r="C39" s="94" t="n">
+      <c r="D39" s="94" t="n">
         <v>-7.14</v>
-      </c>
-      <c r="D39" s="94" t="n">
-        <v>-6.64</v>
       </c>
       <c r="E39" s="94" t="n">
         <v>-6.64</v>
       </c>
       <c r="F39" s="94" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="G39" s="94" t="n">
         <v>-8.300000000000001</v>
-      </c>
-      <c r="G39" s="94" t="n">
-        <v>-8.58</v>
       </c>
       <c r="H39" s="94" t="n">
         <v>-8.58</v>
       </c>
       <c r="I39" s="94" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="J39" s="94" t="n">
         <v>-7.78</v>
-      </c>
-      <c r="J39" s="94" t="n">
-        <v>-8.09</v>
       </c>
       <c r="K39" s="94" t="n">
         <v>-8.09</v>
       </c>
       <c r="L39" s="94" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="M39" s="94" t="n">
         <v>-6.72</v>
       </c>
-      <c r="M39" s="94" t="n">
+      <c r="N39" s="94" t="n">
         <v>-5.16</v>
       </c>
-      <c r="N39" s="94" t="n">
+      <c r="O39" s="94" t="n">
         <v>-3.01</v>
       </c>
-      <c r="O39" s="94" t="n">
+      <c r="P39" s="94" t="n">
         <v>-1.45</v>
-      </c>
-      <c r="P39" s="94" t="n">
-        <v>-1.14</v>
       </c>
       <c r="Q39" s="94" t="n">
         <v>-1.14</v>
       </c>
       <c r="R39" s="94" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="S39" s="94" t="n">
         <v>-2.05</v>
       </c>
-      <c r="S39" s="94" t="n">
+      <c r="T39" s="94" t="n">
         <v>-1.65</v>
       </c>
-      <c r="T39" s="94" t="n">
+      <c r="U39" s="94" t="n">
         <v>-1.75</v>
       </c>
-      <c r="U39" s="94" t="n">
+      <c r="V39" s="94" t="n">
         <v>-0.02</v>
-      </c>
-      <c r="V39" s="94" t="n">
-        <v>-0.26</v>
       </c>
       <c r="W39" s="94" t="n">
         <v>-0.26</v>
       </c>
       <c r="X39" s="94" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Y39" s="94" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y39" s="94" t="n">
+      <c r="Z39" s="94" t="n">
         <v>-0.28</v>
       </c>
-      <c r="Z39" s="94" t="n">
+      <c r="AA39" s="94" t="n">
         <v>-1.65</v>
       </c>
-      <c r="AA39" s="94" t="n">
+      <c r="AB39" s="94" t="n">
         <v>-2.56</v>
-      </c>
-      <c r="AB39" s="94" t="n">
-        <v>-3.33</v>
       </c>
       <c r="AC39" s="94" t="n">
         <v>-3.33</v>
       </c>
       <c r="AD39" s="94" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="AE39" s="94" t="n">
         <v>-4.26</v>
-      </c>
-      <c r="AE39" s="94" t="n">
-        <v>-2.59</v>
       </c>
     </row>
     <row r="40">
@@ -10784,94 +10778,94 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="C40" s="94" t="n">
         <v>-2.75</v>
       </c>
-      <c r="C40" s="94" t="n">
+      <c r="D40" s="94" t="n">
         <v>-2.14</v>
-      </c>
-      <c r="D40" s="94" t="n">
-        <v>-1.62</v>
       </c>
       <c r="E40" s="94" t="n">
         <v>-1.62</v>
       </c>
       <c r="F40" s="94" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="G40" s="94" t="n">
         <v>-1.97</v>
-      </c>
-      <c r="G40" s="94" t="n">
-        <v>-1.89</v>
       </c>
       <c r="H40" s="94" t="n">
         <v>-1.89</v>
       </c>
       <c r="I40" s="94" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="J40" s="94" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="J40" s="94" t="n">
-        <v>-1.81</v>
       </c>
       <c r="K40" s="94" t="n">
         <v>-1.81</v>
       </c>
       <c r="L40" s="94" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="M40" s="94" t="n">
         <v>0.23</v>
       </c>
-      <c r="M40" s="94" t="n">
+      <c r="N40" s="94" t="n">
         <v>1.18</v>
       </c>
-      <c r="N40" s="94" t="n">
+      <c r="O40" s="94" t="n">
         <v>2.56</v>
       </c>
-      <c r="O40" s="94" t="n">
+      <c r="P40" s="94" t="n">
         <v>4.73</v>
-      </c>
-      <c r="P40" s="94" t="n">
-        <v>6.2</v>
       </c>
       <c r="Q40" s="94" t="n">
         <v>6.2</v>
       </c>
       <c r="R40" s="94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S40" s="94" t="n">
         <v>5.28</v>
       </c>
-      <c r="S40" s="94" t="n">
+      <c r="T40" s="94" t="n">
         <v>5.22</v>
       </c>
-      <c r="T40" s="94" t="n">
+      <c r="U40" s="94" t="n">
         <v>5.4</v>
       </c>
-      <c r="U40" s="94" t="n">
+      <c r="V40" s="94" t="n">
         <v>5.44</v>
-      </c>
-      <c r="V40" s="94" t="n">
-        <v>6.13</v>
       </c>
       <c r="W40" s="94" t="n">
         <v>6.13</v>
       </c>
       <c r="X40" s="94" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="Y40" s="94" t="n">
         <v>6.45</v>
       </c>
-      <c r="Y40" s="94" t="n">
+      <c r="Z40" s="94" t="n">
         <v>5.68</v>
       </c>
-      <c r="Z40" s="94" t="n">
+      <c r="AA40" s="94" t="n">
         <v>5.74</v>
       </c>
-      <c r="AA40" s="94" t="n">
+      <c r="AB40" s="94" t="n">
         <v>4.91</v>
-      </c>
-      <c r="AB40" s="94" t="n">
-        <v>4.05</v>
       </c>
       <c r="AC40" s="94" t="n">
         <v>4.05</v>
       </c>
       <c r="AD40" s="94" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE40" s="94" t="n">
         <v>5.29</v>
-      </c>
-      <c r="AE40" s="94" t="n">
-        <v>7.87</v>
       </c>
     </row>
     <row r="41">
@@ -10881,19 +10875,19 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" s="94" t="n">
         <v>33.12</v>
       </c>
-      <c r="C41" s="94" t="n">
+      <c r="D41" s="94" t="n">
         <v>34</v>
-      </c>
-      <c r="D41" s="94" t="n">
-        <v>37.69</v>
       </c>
       <c r="E41" s="94" t="n">
         <v>37.69</v>
       </c>
       <c r="F41" s="94" t="n">
-        <v>34.47</v>
+        <v>37.69</v>
       </c>
       <c r="G41" s="94" t="n">
         <v>34.47</v>
@@ -10902,73 +10896,73 @@
         <v>34.47</v>
       </c>
       <c r="I41" s="94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="J41" s="94" t="n">
         <v>34.91</v>
-      </c>
-      <c r="J41" s="94" t="n">
-        <v>28.94</v>
       </c>
       <c r="K41" s="94" t="n">
         <v>28.94</v>
       </c>
       <c r="L41" s="94" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M41" s="94" t="n">
         <v>35.94</v>
       </c>
-      <c r="M41" s="94" t="n">
+      <c r="N41" s="94" t="n">
         <v>43.73</v>
       </c>
-      <c r="N41" s="94" t="n">
+      <c r="O41" s="94" t="n">
         <v>48.68</v>
       </c>
-      <c r="O41" s="94" t="n">
+      <c r="P41" s="94" t="n">
         <v>62.08</v>
-      </c>
-      <c r="P41" s="94" t="n">
-        <v>68.18000000000001</v>
       </c>
       <c r="Q41" s="94" t="n">
         <v>68.18000000000001</v>
       </c>
       <c r="R41" s="94" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="S41" s="94" t="n">
         <v>60.52</v>
       </c>
-      <c r="S41" s="94" t="n">
+      <c r="T41" s="94" t="n">
         <v>64.43000000000001</v>
       </c>
-      <c r="T41" s="94" t="n">
+      <c r="U41" s="94" t="n">
         <v>64.29000000000001</v>
       </c>
-      <c r="U41" s="94" t="n">
+      <c r="V41" s="94" t="n">
         <v>64.28</v>
-      </c>
-      <c r="V41" s="94" t="n">
-        <v>66.97</v>
       </c>
       <c r="W41" s="94" t="n">
         <v>66.97</v>
       </c>
       <c r="X41" s="94" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="Y41" s="94" t="n">
         <v>67.69</v>
       </c>
-      <c r="Y41" s="94" t="n">
+      <c r="Z41" s="94" t="n">
         <v>62.51</v>
       </c>
-      <c r="Z41" s="94" t="n">
+      <c r="AA41" s="94" t="n">
         <v>61.75</v>
       </c>
-      <c r="AA41" s="94" t="n">
+      <c r="AB41" s="94" t="n">
         <v>57.6</v>
-      </c>
-      <c r="AB41" s="94" t="n">
-        <v>54.27</v>
       </c>
       <c r="AC41" s="94" t="n">
         <v>54.27</v>
       </c>
       <c r="AD41" s="94" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="AE41" s="94" t="n">
         <v>48.01</v>
-      </c>
-      <c r="AE41" s="94" t="n">
-        <v>59.51</v>
       </c>
     </row>
     <row r="42">
@@ -10982,149 +10976,149 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="C42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D42" s="92" t="inlineStr">
+      <c r="E42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="92" t="inlineStr">
+      <c r="F42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="91" t="inlineStr">
+      <c r="G42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="91" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="I42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="91" t="inlineStr">
+      <c r="J42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="91" t="inlineStr">
+      <c r="K42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="91" t="inlineStr">
+      <c r="L42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="91" t="inlineStr">
+      <c r="M42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="91" t="inlineStr">
+      <c r="P42" s="91" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P42" s="93" t="inlineStr">
+      <c r="Q42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="93" t="inlineStr">
+      <c r="R42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="93" t="inlineStr">
+      <c r="S42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S42" s="93" t="inlineStr">
+      <c r="T42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T42" s="93" t="inlineStr">
+      <c r="U42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U42" s="92" t="inlineStr">
+      <c r="V42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V42" s="92" t="inlineStr">
+      <c r="W42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W42" s="92" t="inlineStr">
+      <c r="X42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="92" t="inlineStr">
+      <c r="Y42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="92" t="inlineStr">
+      <c r="Z42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="92" t="inlineStr">
+      <c r="AA42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="93" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="93" t="inlineStr">
+      <c r="AC42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC42" s="93" t="inlineStr">
+      <c r="AD42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD42" s="93" t="inlineStr">
+      <c r="AE42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -11138,16 +11132,16 @@
         <v>-2.13</v>
       </c>
       <c r="C43" s="94" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="D43" s="94" t="n">
         <v>-2.2</v>
-      </c>
-      <c r="D43" s="94" t="n">
-        <v>-2.93</v>
       </c>
       <c r="E43" s="94" t="n">
         <v>-2.93</v>
       </c>
       <c r="F43" s="94" t="n">
-        <v>-3.85</v>
+        <v>-2.93</v>
       </c>
       <c r="G43" s="94" t="n">
         <v>-3.85</v>
@@ -11156,73 +11150,73 @@
         <v>-3.85</v>
       </c>
       <c r="I43" s="94" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="J43" s="94" t="n">
         <v>-4.76</v>
-      </c>
-      <c r="J43" s="94" t="n">
-        <v>-6.64</v>
       </c>
       <c r="K43" s="94" t="n">
         <v>-6.64</v>
       </c>
       <c r="L43" s="94" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="M43" s="94" t="n">
         <v>-5.78</v>
       </c>
-      <c r="M43" s="94" t="n">
+      <c r="N43" s="94" t="n">
         <v>-2.39</v>
       </c>
-      <c r="N43" s="94" t="n">
+      <c r="O43" s="94" t="n">
         <v>-3.13</v>
       </c>
-      <c r="O43" s="94" t="n">
+      <c r="P43" s="94" t="n">
         <v>-2.01</v>
-      </c>
-      <c r="P43" s="94" t="n">
-        <v>-1.21</v>
       </c>
       <c r="Q43" s="94" t="n">
         <v>-1.21</v>
       </c>
       <c r="R43" s="94" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="S43" s="94" t="n">
         <v>-2.55</v>
       </c>
-      <c r="S43" s="94" t="n">
+      <c r="T43" s="94" t="n">
         <v>-0.29</v>
       </c>
-      <c r="T43" s="94" t="n">
+      <c r="U43" s="94" t="n">
         <v>-1.24</v>
       </c>
-      <c r="U43" s="94" t="n">
+      <c r="V43" s="94" t="n">
         <v>0.41</v>
-      </c>
-      <c r="V43" s="94" t="n">
-        <v>-0.51</v>
       </c>
       <c r="W43" s="94" t="n">
         <v>-0.51</v>
       </c>
       <c r="X43" s="94" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="Y43" s="94" t="n">
         <v>-1.41</v>
       </c>
-      <c r="Y43" s="94" t="n">
+      <c r="Z43" s="94" t="n">
         <v>-1.26</v>
       </c>
-      <c r="Z43" s="94" t="n">
+      <c r="AA43" s="94" t="n">
         <v>-2.05</v>
       </c>
-      <c r="AA43" s="94" t="n">
+      <c r="AB43" s="94" t="n">
         <v>-2.54</v>
-      </c>
-      <c r="AB43" s="94" t="n">
-        <v>-1.59</v>
       </c>
       <c r="AC43" s="94" t="n">
         <v>-1.59</v>
       </c>
       <c r="AD43" s="94" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="AE43" s="94" t="n">
         <v>-3.4</v>
-      </c>
-      <c r="AE43" s="94" t="n">
-        <v>-4.77</v>
       </c>
     </row>
     <row r="44">
@@ -11235,16 +11229,16 @@
         <v>-4.45</v>
       </c>
       <c r="C44" s="94" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="D44" s="94" t="n">
         <v>-4.11</v>
-      </c>
-      <c r="D44" s="94" t="n">
-        <v>-2.88</v>
       </c>
       <c r="E44" s="94" t="n">
         <v>-2.88</v>
       </c>
       <c r="F44" s="94" t="n">
-        <v>-3.01</v>
+        <v>-2.88</v>
       </c>
       <c r="G44" s="94" t="n">
         <v>-3.01</v>
@@ -11253,73 +11247,73 @@
         <v>-3.01</v>
       </c>
       <c r="I44" s="94" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="J44" s="94" t="n">
         <v>-4.66</v>
-      </c>
-      <c r="J44" s="94" t="n">
-        <v>-5.23</v>
       </c>
       <c r="K44" s="94" t="n">
         <v>-5.23</v>
       </c>
       <c r="L44" s="94" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="M44" s="94" t="n">
         <v>-5.22</v>
       </c>
-      <c r="M44" s="94" t="n">
+      <c r="N44" s="94" t="n">
         <v>-3.24</v>
       </c>
-      <c r="N44" s="94" t="n">
+      <c r="O44" s="94" t="n">
         <v>-2.29</v>
       </c>
-      <c r="O44" s="94" t="n">
+      <c r="P44" s="94" t="n">
         <v>-2.7</v>
-      </c>
-      <c r="P44" s="94" t="n">
-        <v>-0.93</v>
       </c>
       <c r="Q44" s="94" t="n">
         <v>-0.93</v>
       </c>
       <c r="R44" s="94" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="S44" s="94" t="n">
         <v>-1.46</v>
       </c>
-      <c r="S44" s="94" t="n">
+      <c r="T44" s="94" t="n">
         <v>-2.44</v>
       </c>
-      <c r="T44" s="94" t="n">
+      <c r="U44" s="94" t="n">
         <v>-3.49</v>
       </c>
-      <c r="U44" s="94" t="n">
+      <c r="V44" s="94" t="n">
         <v>-2.94</v>
-      </c>
-      <c r="V44" s="94" t="n">
-        <v>-2.64</v>
       </c>
       <c r="W44" s="94" t="n">
         <v>-2.64</v>
       </c>
       <c r="X44" s="94" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="Y44" s="94" t="n">
         <v>-4.44</v>
       </c>
-      <c r="Y44" s="94" t="n">
+      <c r="Z44" s="94" t="n">
         <v>-3.53</v>
       </c>
-      <c r="Z44" s="94" t="n">
+      <c r="AA44" s="94" t="n">
         <v>-4.89</v>
       </c>
-      <c r="AA44" s="94" t="n">
+      <c r="AB44" s="94" t="n">
         <v>-4.42</v>
-      </c>
-      <c r="AB44" s="94" t="n">
-        <v>-3.57</v>
       </c>
       <c r="AC44" s="94" t="n">
         <v>-3.57</v>
       </c>
       <c r="AD44" s="94" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="AE44" s="94" t="n">
         <v>-6.86</v>
-      </c>
-      <c r="AE44" s="94" t="n">
-        <v>-9.18</v>
       </c>
     </row>
     <row r="45">
@@ -11332,16 +11326,16 @@
         <v>63.25</v>
       </c>
       <c r="C45" s="94" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="D45" s="94" t="n">
         <v>46.49</v>
-      </c>
-      <c r="D45" s="94" t="n">
-        <v>60.14</v>
       </c>
       <c r="E45" s="94" t="n">
         <v>60.14</v>
       </c>
       <c r="F45" s="94" t="n">
-        <v>32.65</v>
+        <v>60.14</v>
       </c>
       <c r="G45" s="94" t="n">
         <v>32.65</v>
@@ -11350,73 +11344,73 @@
         <v>32.65</v>
       </c>
       <c r="I45" s="94" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="J45" s="94" t="n">
         <v>26.89</v>
-      </c>
-      <c r="J45" s="94" t="n">
-        <v>27.28</v>
       </c>
       <c r="K45" s="94" t="n">
         <v>27.28</v>
       </c>
       <c r="L45" s="94" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="M45" s="94" t="n">
         <v>30.52</v>
       </c>
-      <c r="M45" s="94" t="n">
+      <c r="N45" s="94" t="n">
         <v>53.78</v>
       </c>
-      <c r="N45" s="94" t="n">
+      <c r="O45" s="94" t="n">
         <v>47.01</v>
       </c>
-      <c r="O45" s="94" t="n">
+      <c r="P45" s="94" t="n">
         <v>44.02</v>
-      </c>
-      <c r="P45" s="94" t="n">
-        <v>60.7</v>
       </c>
       <c r="Q45" s="94" t="n">
         <v>60.7</v>
       </c>
       <c r="R45" s="94" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="S45" s="94" t="n">
         <v>64.97</v>
       </c>
-      <c r="S45" s="94" t="n">
+      <c r="T45" s="94" t="n">
         <v>65.77</v>
       </c>
-      <c r="T45" s="94" t="n">
+      <c r="U45" s="94" t="n">
         <v>61.34</v>
       </c>
-      <c r="U45" s="94" t="n">
+      <c r="V45" s="94" t="n">
         <v>88.75</v>
-      </c>
-      <c r="V45" s="94" t="n">
-        <v>85.52</v>
       </c>
       <c r="W45" s="94" t="n">
         <v>85.52</v>
       </c>
       <c r="X45" s="94" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="Y45" s="94" t="n">
         <v>75.22</v>
       </c>
-      <c r="Y45" s="94" t="n">
+      <c r="Z45" s="94" t="n">
         <v>70.47</v>
       </c>
-      <c r="Z45" s="94" t="n">
+      <c r="AA45" s="94" t="n">
         <v>59.59</v>
       </c>
-      <c r="AA45" s="94" t="n">
+      <c r="AB45" s="94" t="n">
         <v>54.39</v>
-      </c>
-      <c r="AB45" s="94" t="n">
-        <v>53.93</v>
       </c>
       <c r="AC45" s="94" t="n">
         <v>53.93</v>
       </c>
       <c r="AD45" s="94" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="AE45" s="94" t="n">
         <v>38.48</v>
-      </c>
-      <c r="AE45" s="94" t="n">
-        <v>25.53</v>
       </c>
     </row>
     <row r="46">
@@ -11480,99 +11474,99 @@
           <t>green</t>
         </is>
       </c>
-      <c r="M46" s="93" t="inlineStr">
+      <c r="M46" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="O46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="P46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P46" s="93" t="inlineStr">
+      <c r="Q46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q46" s="93" t="inlineStr">
+      <c r="R46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R46" s="93" t="inlineStr">
+      <c r="S46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S46" s="93" t="inlineStr">
+      <c r="T46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T46" s="93" t="inlineStr">
+      <c r="U46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U46" s="93" t="inlineStr">
+      <c r="V46" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V46" s="92" t="inlineStr">
+      <c r="W46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="X46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X46" s="92" t="inlineStr">
+      <c r="Y46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y46" s="92" t="inlineStr">
+      <c r="Z46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z46" s="92" t="inlineStr">
+      <c r="AA46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA46" s="92" t="inlineStr">
+      <c r="AB46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB46" s="92" t="inlineStr">
+      <c r="AC46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC46" s="92" t="inlineStr">
+      <c r="AD46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD46" s="92" t="inlineStr">
+      <c r="AE46" s="92" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -11589,13 +11583,13 @@
         <v>3.88</v>
       </c>
       <c r="D47" s="94" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="E47" s="94" t="n">
         <v>4.01</v>
       </c>
       <c r="F47" s="94" t="n">
-        <v>2.71</v>
+        <v>4.01</v>
       </c>
       <c r="G47" s="94" t="n">
         <v>2.71</v>
@@ -11607,70 +11601,70 @@
         <v>2.71</v>
       </c>
       <c r="J47" s="94" t="n">
-        <v>2.11</v>
+        <v>2.71</v>
       </c>
       <c r="K47" s="94" t="n">
         <v>2.11</v>
       </c>
       <c r="L47" s="94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M47" s="94" t="n">
         <v>3.8</v>
       </c>
-      <c r="M47" s="94" t="n">
+      <c r="N47" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="N47" s="94" t="n">
+      <c r="O47" s="94" t="n">
         <v>6.58</v>
       </c>
-      <c r="O47" s="94" t="n">
+      <c r="P47" s="94" t="n">
         <v>7.78</v>
-      </c>
-      <c r="P47" s="94" t="n">
-        <v>9.01</v>
       </c>
       <c r="Q47" s="94" t="n">
         <v>9.01</v>
       </c>
       <c r="R47" s="94" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="S47" s="94" t="n">
         <v>7.49</v>
       </c>
-      <c r="S47" s="94" t="n">
+      <c r="T47" s="94" t="n">
         <v>9.02</v>
       </c>
-      <c r="T47" s="94" t="n">
+      <c r="U47" s="94" t="n">
         <v>8.56</v>
       </c>
-      <c r="U47" s="94" t="n">
+      <c r="V47" s="94" t="n">
         <v>9.19</v>
-      </c>
-      <c r="V47" s="94" t="n">
-        <v>9.01</v>
       </c>
       <c r="W47" s="94" t="n">
         <v>9.01</v>
       </c>
       <c r="X47" s="94" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="Y47" s="94" t="n">
         <v>9.94</v>
       </c>
-      <c r="Y47" s="94" t="n">
+      <c r="Z47" s="94" t="n">
         <v>10.38</v>
       </c>
-      <c r="Z47" s="94" t="n">
+      <c r="AA47" s="94" t="n">
         <v>9.59</v>
       </c>
-      <c r="AA47" s="94" t="n">
+      <c r="AB47" s="94" t="n">
         <v>8.08</v>
-      </c>
-      <c r="AB47" s="94" t="n">
-        <v>7.24</v>
       </c>
       <c r="AC47" s="94" t="n">
         <v>7.24</v>
       </c>
       <c r="AD47" s="94" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AE47" s="94" t="n">
         <v>4.57</v>
-      </c>
-      <c r="AE47" s="94" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="48">
@@ -11686,13 +11680,13 @@
         <v>8.16</v>
       </c>
       <c r="D48" s="94" t="n">
-        <v>9.59</v>
+        <v>8.16</v>
       </c>
       <c r="E48" s="94" t="n">
         <v>9.59</v>
       </c>
       <c r="F48" s="94" t="n">
-        <v>7.45</v>
+        <v>9.59</v>
       </c>
       <c r="G48" s="94" t="n">
         <v>7.45</v>
@@ -11704,70 +11698,70 @@
         <v>7.45</v>
       </c>
       <c r="J48" s="94" t="n">
-        <v>7.63</v>
+        <v>7.45</v>
       </c>
       <c r="K48" s="94" t="n">
         <v>7.63</v>
       </c>
       <c r="L48" s="94" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M48" s="94" t="n">
         <v>8.23</v>
       </c>
-      <c r="M48" s="94" t="n">
+      <c r="N48" s="94" t="n">
         <v>10.17</v>
       </c>
-      <c r="N48" s="94" t="n">
+      <c r="O48" s="94" t="n">
         <v>11.46</v>
       </c>
-      <c r="O48" s="94" t="n">
+      <c r="P48" s="94" t="n">
         <v>11.06</v>
-      </c>
-      <c r="P48" s="94" t="n">
-        <v>11.9</v>
       </c>
       <c r="Q48" s="94" t="n">
         <v>11.9</v>
       </c>
       <c r="R48" s="94" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S48" s="94" t="n">
         <v>12.17</v>
       </c>
-      <c r="S48" s="94" t="n">
+      <c r="T48" s="94" t="n">
         <v>12.36</v>
       </c>
-      <c r="T48" s="94" t="n">
+      <c r="U48" s="94" t="n">
         <v>11.84</v>
       </c>
-      <c r="U48" s="94" t="n">
+      <c r="V48" s="94" t="n">
         <v>11.02</v>
-      </c>
-      <c r="V48" s="94" t="n">
-        <v>12.23</v>
       </c>
       <c r="W48" s="94" t="n">
         <v>12.23</v>
       </c>
       <c r="X48" s="94" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="Y48" s="94" t="n">
         <v>11.53</v>
       </c>
-      <c r="Y48" s="94" t="n">
+      <c r="Z48" s="94" t="n">
         <v>11.98</v>
       </c>
-      <c r="Z48" s="94" t="n">
+      <c r="AA48" s="94" t="n">
         <v>10.39</v>
       </c>
-      <c r="AA48" s="94" t="n">
+      <c r="AB48" s="94" t="n">
         <v>10.32</v>
-      </c>
-      <c r="AB48" s="94" t="n">
-        <v>9.02</v>
       </c>
       <c r="AC48" s="94" t="n">
         <v>9.02</v>
       </c>
       <c r="AD48" s="94" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AE48" s="94" t="n">
         <v>6.35</v>
-      </c>
-      <c r="AE48" s="94" t="n">
-        <v>3.39</v>
       </c>
     </row>
     <row r="49">
@@ -11783,13 +11777,13 @@
         <v>35.85</v>
       </c>
       <c r="D49" s="94" t="n">
-        <v>41.58</v>
+        <v>35.85</v>
       </c>
       <c r="E49" s="94" t="n">
         <v>41.58</v>
       </c>
       <c r="F49" s="94" t="n">
-        <v>23.15</v>
+        <v>41.58</v>
       </c>
       <c r="G49" s="94" t="n">
         <v>23.15</v>
@@ -11801,76 +11795,76 @@
         <v>23.15</v>
       </c>
       <c r="J49" s="94" t="n">
-        <v>24.88</v>
+        <v>23.15</v>
       </c>
       <c r="K49" s="94" t="n">
         <v>24.88</v>
       </c>
       <c r="L49" s="94" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="M49" s="94" t="n">
         <v>29.2</v>
       </c>
-      <c r="M49" s="94" t="n">
+      <c r="N49" s="94" t="n">
         <v>54.41</v>
       </c>
-      <c r="N49" s="94" t="n">
+      <c r="O49" s="94" t="n">
         <v>54.96</v>
       </c>
-      <c r="O49" s="94" t="n">
+      <c r="P49" s="94" t="n">
         <v>64.64</v>
-      </c>
-      <c r="P49" s="94" t="n">
-        <v>80.84999999999999</v>
       </c>
       <c r="Q49" s="94" t="n">
         <v>80.84999999999999</v>
       </c>
       <c r="R49" s="94" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="S49" s="94" t="n">
         <v>84.77</v>
       </c>
-      <c r="S49" s="94" t="n">
+      <c r="T49" s="94" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="T49" s="94" t="n">
+      <c r="U49" s="94" t="n">
         <v>81.66</v>
       </c>
-      <c r="U49" s="94" t="n">
+      <c r="V49" s="94" t="n">
         <v>84</v>
-      </c>
-      <c r="V49" s="94" t="n">
-        <v>88.88</v>
       </c>
       <c r="W49" s="94" t="n">
         <v>88.88</v>
       </c>
       <c r="X49" s="94" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="Y49" s="94" t="n">
         <v>88.51000000000001</v>
       </c>
-      <c r="Y49" s="94" t="n">
+      <c r="Z49" s="94" t="n">
         <v>86.69</v>
       </c>
-      <c r="Z49" s="94" t="n">
+      <c r="AA49" s="94" t="n">
         <v>82.84</v>
       </c>
-      <c r="AA49" s="94" t="n">
+      <c r="AB49" s="94" t="n">
         <v>81.08</v>
-      </c>
-      <c r="AB49" s="94" t="n">
-        <v>72.36</v>
       </c>
       <c r="AC49" s="94" t="n">
         <v>72.36</v>
       </c>
       <c r="AD49" s="94" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="AE49" s="94" t="n">
         <v>63.1</v>
-      </c>
-      <c r="AE49" s="94" t="n">
-        <v>52.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：cy:RNG60:-16.02&lt;=-10;us500:RS2:11.56&lt;=22;us30:RS3:22.32&lt;=25;ixic:RS2:6.54&lt;=38;sensex:RS10:33.12&lt;=39</t>
+          <t>今日买报：cy:RNG60:-16.02&lt;=-10;us500:RS2:7.97&lt;=22;us30:RS3:21.31&lt;=25;ixic:RS2:6.54&lt;=38;sensex:RS10:39.0&lt;=39</t>
         </is>
       </c>
     </row>
